--- a/description/TC 설계서.xlsx
+++ b/description/TC 설계서.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suresoft\Documents\study_docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suresoft\Documents\sure_rust_project\description\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD489691-9168-431C-A4AB-398668C75818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5763C3AF-16BC-4C5E-BE5A-0D627C7D5739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41940" yWindow="3150" windowWidth="25065" windowHeight="17025" tabRatio="291" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44955" yWindow="4080" windowWidth="20055" windowHeight="13620" tabRatio="291" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="최소 TC 조합" sheetId="4" r:id="rId1"/>
@@ -4267,14 +4267,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4291,11 +4285,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4315,6 +4312,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4327,23 +4342,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4352,18 +4364,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4695,835 +4695,835 @@
       </c>
     </row>
     <row r="3" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="55" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="D3" s="39" t="s">
         <v>145</v>
       </c>
       <c r="E3" s="27" t="s">
         <v>289</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="F3" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G3" s="43">
+      <c r="G3" s="41">
         <v>4</v>
       </c>
-      <c r="H3" s="41" t="s">
+      <c r="H3" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="I3" s="44" t="s">
+      <c r="I3" s="42" t="s">
         <v>294</v>
       </c>
-      <c r="J3" s="37" t="s">
+      <c r="J3" s="43" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B4" s="38"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
       <c r="E4" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="37"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="43"/>
     </row>
     <row r="5" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B5" s="38"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
       <c r="E5" s="27" t="s">
         <v>277</v>
       </c>
-      <c r="F5" s="42"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="37"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
     </row>
     <row r="6" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B6" s="38"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
       <c r="E6" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="37"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="43"/>
     </row>
     <row r="7" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B7" s="38"/>
-      <c r="C7" s="40" t="s">
+      <c r="B7" s="55"/>
+      <c r="C7" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="38" t="s">
         <v>144</v>
       </c>
       <c r="E7" s="27" t="s">
         <v>289</v>
       </c>
-      <c r="F7" s="42" t="s">
+      <c r="F7" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G7" s="43">
+      <c r="G7" s="41">
         <v>4</v>
       </c>
-      <c r="H7" s="41" t="s">
+      <c r="H7" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="I7" s="44" t="s">
+      <c r="I7" s="42" t="s">
         <v>295</v>
       </c>
-      <c r="J7" s="37" t="s">
+      <c r="J7" s="43" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B8" s="38"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
       <c r="E8" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="37"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="43"/>
     </row>
     <row r="9" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B9" s="38"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
+      <c r="B9" s="55"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
       <c r="E9" s="27" t="s">
         <v>278</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="37"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="43"/>
     </row>
     <row r="10" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B10" s="38"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
       <c r="E10" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="F10" s="42"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="37"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="43"/>
     </row>
     <row r="11" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B11" s="38"/>
-      <c r="C11" s="40" t="s">
+      <c r="B11" s="55"/>
+      <c r="C11" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="D11" s="40" t="s">
+      <c r="D11" s="38" t="s">
         <v>153</v>
       </c>
       <c r="E11" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="F11" s="42" t="s">
+      <c r="F11" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G11" s="43">
+      <c r="G11" s="41">
         <v>4</v>
       </c>
-      <c r="H11" s="41" t="s">
+      <c r="H11" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="I11" s="44" t="s">
+      <c r="I11" s="42" t="s">
         <v>296</v>
       </c>
-      <c r="J11" s="37" t="s">
+      <c r="J11" s="43" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B12" s="38"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
       <c r="E12" s="27" t="s">
         <v>279</v>
       </c>
-      <c r="F12" s="42"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="37"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="43"/>
     </row>
     <row r="13" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B13" s="38"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
       <c r="E13" s="27" t="s">
         <v>277</v>
       </c>
-      <c r="F13" s="42"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="37"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="43"/>
     </row>
     <row r="14" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B14" s="38"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
       <c r="E14" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="F14" s="42"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="37"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="43"/>
     </row>
     <row r="15" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B15" s="38"/>
-      <c r="C15" s="40" t="s">
+      <c r="B15" s="55"/>
+      <c r="C15" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="D15" s="40" t="s">
+      <c r="D15" s="38" t="s">
         <v>154</v>
       </c>
       <c r="E15" s="27" t="s">
         <v>289</v>
       </c>
-      <c r="F15" s="42" t="s">
+      <c r="F15" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G15" s="43">
+      <c r="G15" s="41">
         <v>4</v>
       </c>
-      <c r="H15" s="41" t="s">
+      <c r="H15" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="I15" s="44" t="s">
+      <c r="I15" s="42" t="s">
         <v>297</v>
       </c>
-      <c r="J15" s="37" t="s">
+      <c r="J15" s="43" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B16" s="38"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
       <c r="E16" s="27" t="s">
         <v>279</v>
       </c>
-      <c r="F16" s="42"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="37"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="43"/>
     </row>
     <row r="17" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B17" s="38"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
       <c r="E17" s="27" t="s">
         <v>277</v>
       </c>
-      <c r="F17" s="42"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="37"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="43"/>
     </row>
     <row r="18" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B18" s="39"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
       <c r="E18" s="26" t="s">
         <v>227</v>
       </c>
-      <c r="F18" s="54"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="56"/>
-      <c r="I18" s="57"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="44"/>
       <c r="J18" s="45"/>
     </row>
     <row r="19" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="62" t="s">
         <v>141</v>
       </c>
-      <c r="C19" s="47" t="s">
+      <c r="C19" s="46" t="s">
         <v>115</v>
       </c>
-      <c r="D19" s="48" t="s">
+      <c r="D19" s="47" t="s">
         <v>147</v>
       </c>
       <c r="E19" s="27" t="s">
         <v>289</v>
       </c>
-      <c r="F19" s="49" t="s">
+      <c r="F19" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="G19" s="50">
+      <c r="G19" s="49">
         <v>4</v>
       </c>
-      <c r="H19" s="48" t="s">
+      <c r="H19" s="47" t="s">
         <v>128</v>
       </c>
-      <c r="I19" s="51" t="s">
+      <c r="I19" s="50" t="s">
         <v>298</v>
       </c>
-      <c r="J19" s="52" t="s">
+      <c r="J19" s="51" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="20" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B20" s="38"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="41"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="39"/>
       <c r="E20" s="27" t="s">
         <v>280</v>
       </c>
-      <c r="F20" s="42"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="37"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="43"/>
     </row>
     <row r="21" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B21" s="38"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
       <c r="E21" s="25" t="s">
         <v>281</v>
       </c>
-      <c r="F21" s="42"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="37"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="43"/>
     </row>
     <row r="22" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B22" s="38"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
       <c r="E22" s="27" t="s">
         <v>282</v>
       </c>
-      <c r="F22" s="42"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="37"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="43"/>
     </row>
     <row r="23" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B23" s="38"/>
-      <c r="C23" s="40" t="s">
+      <c r="B23" s="55"/>
+      <c r="C23" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="D23" s="41" t="s">
+      <c r="D23" s="39" t="s">
         <v>149</v>
       </c>
       <c r="E23" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="F23" s="42" t="s">
+      <c r="F23" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G23" s="43">
+      <c r="G23" s="41">
         <v>4</v>
       </c>
-      <c r="H23" s="41" t="s">
+      <c r="H23" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="I23" s="44" t="s">
+      <c r="I23" s="42" t="s">
         <v>299</v>
       </c>
-      <c r="J23" s="37" t="s">
+      <c r="J23" s="43" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="24" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B24" s="38"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="41"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="39"/>
       <c r="E24" s="27" t="s">
         <v>280</v>
       </c>
-      <c r="F24" s="42"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="37"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="43"/>
     </row>
     <row r="25" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B25" s="38"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
       <c r="E25" s="25" t="s">
         <v>281</v>
       </c>
-      <c r="F25" s="42"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="44"/>
-      <c r="J25" s="37"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="43"/>
     </row>
     <row r="26" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B26" s="38"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
+      <c r="B26" s="55"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
       <c r="E26" s="27" t="s">
         <v>283</v>
       </c>
-      <c r="F26" s="42"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="44"/>
-      <c r="J26" s="37"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="43"/>
     </row>
     <row r="27" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B27" s="38"/>
-      <c r="C27" s="40" t="s">
+      <c r="B27" s="55"/>
+      <c r="C27" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="D27" s="40" t="s">
+      <c r="D27" s="38" t="s">
         <v>122</v>
       </c>
       <c r="E27" s="27" t="s">
         <v>289</v>
       </c>
-      <c r="F27" s="42" t="s">
+      <c r="F27" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G27" s="43">
+      <c r="G27" s="41">
         <v>4</v>
       </c>
-      <c r="H27" s="41" t="s">
+      <c r="H27" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="I27" s="44" t="s">
+      <c r="I27" s="42" t="s">
         <v>300</v>
       </c>
-      <c r="J27" s="37" t="s">
+      <c r="J27" s="43" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="28" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B28" s="38"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
       <c r="E28" s="27" t="s">
         <v>280</v>
       </c>
-      <c r="F28" s="42"/>
-      <c r="G28" s="43"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="37"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="43"/>
     </row>
     <row r="29" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B29" s="38"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
+      <c r="B29" s="55"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
       <c r="E29" s="25" t="s">
         <v>284</v>
       </c>
-      <c r="F29" s="42"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="37"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="43"/>
     </row>
     <row r="30" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B30" s="39"/>
-      <c r="C30" s="53"/>
-      <c r="D30" s="53"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="58"/>
+      <c r="D30" s="58"/>
       <c r="E30" s="27" t="s">
         <v>283</v>
       </c>
-      <c r="F30" s="54"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="57"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="60"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="44"/>
       <c r="J30" s="45"/>
     </row>
     <row r="31" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B31" s="62" t="s">
+      <c r="B31" s="37" t="s">
         <v>288</v>
       </c>
-      <c r="C31" s="47" t="s">
+      <c r="C31" s="46" t="s">
         <v>162</v>
       </c>
-      <c r="D31" s="48" t="s">
+      <c r="D31" s="47" t="s">
         <v>269</v>
       </c>
       <c r="E31" s="30" t="s">
         <v>181</v>
       </c>
-      <c r="F31" s="49" t="s">
+      <c r="F31" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="G31" s="50">
+      <c r="G31" s="49">
         <v>3</v>
       </c>
-      <c r="H31" s="47" t="s">
+      <c r="H31" s="46" t="s">
         <v>272</v>
       </c>
-      <c r="I31" s="51" t="s">
+      <c r="I31" s="50" t="s">
         <v>301</v>
       </c>
-      <c r="J31" s="52" t="s">
+      <c r="J31" s="51" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="32" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B32" s="62"/>
-      <c r="C32" s="40"/>
-      <c r="D32" s="41"/>
+      <c r="B32" s="37"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="39"/>
       <c r="E32" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="F32" s="42"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="40"/>
-      <c r="I32" s="44"/>
-      <c r="J32" s="37"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="43"/>
     </row>
     <row r="33" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B33" s="62"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="41"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="39"/>
       <c r="E33" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="F33" s="42"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="40"/>
-      <c r="I33" s="44"/>
-      <c r="J33" s="37"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="43"/>
     </row>
     <row r="34" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B34" s="62"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="41"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="39"/>
       <c r="E34" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="F34" s="42"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="40"/>
-      <c r="I34" s="44"/>
-      <c r="J34" s="37"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="43"/>
     </row>
     <row r="35" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B35" s="62"/>
-      <c r="C35" s="40"/>
-      <c r="D35" s="41"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="39"/>
       <c r="E35" s="36" t="s">
         <v>291</v>
       </c>
-      <c r="F35" s="42"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="40"/>
-      <c r="I35" s="44"/>
-      <c r="J35" s="37"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="43"/>
     </row>
     <row r="36" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B36" s="62"/>
-      <c r="C36" s="40" t="s">
+      <c r="B36" s="37"/>
+      <c r="C36" s="38" t="s">
         <v>163</v>
       </c>
-      <c r="D36" s="41" t="s">
+      <c r="D36" s="39" t="s">
         <v>270</v>
       </c>
       <c r="E36" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="F36" s="42" t="s">
+      <c r="F36" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G36" s="43">
+      <c r="G36" s="41">
         <v>5</v>
       </c>
-      <c r="H36" s="40" t="s">
+      <c r="H36" s="38" t="s">
         <v>271</v>
       </c>
-      <c r="I36" s="44" t="s">
+      <c r="I36" s="42" t="s">
         <v>302</v>
       </c>
-      <c r="J36" s="37" t="s">
+      <c r="J36" s="43" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="37" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B37" s="62"/>
-      <c r="C37" s="40"/>
-      <c r="D37" s="41"/>
+      <c r="B37" s="37"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="39"/>
       <c r="E37" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="F37" s="42"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="40"/>
-      <c r="I37" s="44"/>
-      <c r="J37" s="37"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="38"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="43"/>
     </row>
     <row r="38" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B38" s="62"/>
-      <c r="C38" s="40"/>
-      <c r="D38" s="41"/>
+      <c r="B38" s="37"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="39"/>
       <c r="E38" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="F38" s="42"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="40"/>
-      <c r="I38" s="44"/>
-      <c r="J38" s="37"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="43"/>
     </row>
     <row r="39" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B39" s="62"/>
-      <c r="C39" s="40"/>
-      <c r="D39" s="41"/>
+      <c r="B39" s="37"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="39"/>
       <c r="E39" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="F39" s="42"/>
-      <c r="G39" s="43"/>
-      <c r="H39" s="40"/>
-      <c r="I39" s="44"/>
-      <c r="J39" s="37"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="41"/>
+      <c r="H39" s="38"/>
+      <c r="I39" s="42"/>
+      <c r="J39" s="43"/>
     </row>
     <row r="40" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B40" s="62"/>
-      <c r="C40" s="40"/>
-      <c r="D40" s="41"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="39"/>
       <c r="E40" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="F40" s="42"/>
-      <c r="G40" s="43"/>
-      <c r="H40" s="40"/>
-      <c r="I40" s="44"/>
-      <c r="J40" s="37"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="41"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="42"/>
+      <c r="J40" s="43"/>
     </row>
     <row r="41" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B41" s="62"/>
-      <c r="C41" s="40"/>
-      <c r="D41" s="41"/>
+      <c r="B41" s="37"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="39"/>
       <c r="E41" s="36" t="s">
         <v>292</v>
       </c>
-      <c r="F41" s="42"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="40"/>
-      <c r="I41" s="44"/>
-      <c r="J41" s="37"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="42"/>
+      <c r="J41" s="43"/>
     </row>
     <row r="42" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B42" s="62"/>
-      <c r="C42" s="40" t="s">
+      <c r="B42" s="37"/>
+      <c r="C42" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="D42" s="41" t="s">
+      <c r="D42" s="39" t="s">
         <v>172</v>
       </c>
       <c r="E42" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="F42" s="42" t="s">
+      <c r="F42" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G42" s="43">
+      <c r="G42" s="41">
         <v>3</v>
       </c>
-      <c r="H42" s="40" t="s">
+      <c r="H42" s="38" t="s">
         <v>274</v>
       </c>
-      <c r="I42" s="44" t="s">
+      <c r="I42" s="42" t="s">
         <v>303</v>
       </c>
-      <c r="J42" s="37" t="s">
+      <c r="J42" s="43" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="43" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B43" s="62"/>
-      <c r="C43" s="40"/>
-      <c r="D43" s="41"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="39"/>
       <c r="E43" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="F43" s="42"/>
-      <c r="G43" s="43"/>
-      <c r="H43" s="40"/>
-      <c r="I43" s="44"/>
-      <c r="J43" s="37"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="41"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="42"/>
+      <c r="J43" s="43"/>
     </row>
     <row r="44" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B44" s="62"/>
-      <c r="C44" s="40"/>
-      <c r="D44" s="41"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="39"/>
       <c r="E44" s="27" t="s">
         <v>183</v>
       </c>
-      <c r="F44" s="42"/>
-      <c r="G44" s="43"/>
-      <c r="H44" s="40"/>
-      <c r="I44" s="44"/>
-      <c r="J44" s="37"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="43"/>
     </row>
     <row r="45" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B45" s="62"/>
-      <c r="C45" s="40"/>
-      <c r="D45" s="41"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="38"/>
+      <c r="D45" s="39"/>
       <c r="E45" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="F45" s="42"/>
-      <c r="G45" s="43"/>
-      <c r="H45" s="40"/>
-      <c r="I45" s="44"/>
-      <c r="J45" s="37"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="38"/>
+      <c r="I45" s="42"/>
+      <c r="J45" s="43"/>
     </row>
     <row r="46" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B46" s="62"/>
-      <c r="C46" s="40"/>
-      <c r="D46" s="41"/>
+      <c r="B46" s="37"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="39"/>
       <c r="E46" s="36" t="s">
         <v>291</v>
       </c>
-      <c r="F46" s="42"/>
-      <c r="G46" s="43"/>
-      <c r="H46" s="40"/>
-      <c r="I46" s="44"/>
-      <c r="J46" s="37"/>
+      <c r="F46" s="40"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="42"/>
+      <c r="J46" s="43"/>
     </row>
     <row r="47" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B47" s="62"/>
-      <c r="C47" s="40" t="s">
+      <c r="B47" s="37"/>
+      <c r="C47" s="38" t="s">
         <v>166</v>
       </c>
-      <c r="D47" s="41" t="s">
+      <c r="D47" s="39" t="s">
         <v>173</v>
       </c>
       <c r="E47" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="F47" s="42" t="s">
+      <c r="F47" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G47" s="43">
+      <c r="G47" s="41">
         <v>3</v>
       </c>
-      <c r="H47" s="40" t="s">
+      <c r="H47" s="38" t="s">
         <v>273</v>
       </c>
-      <c r="I47" s="44" t="s">
+      <c r="I47" s="42" t="s">
         <v>304</v>
       </c>
-      <c r="J47" s="37" t="s">
+      <c r="J47" s="43" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="48" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B48" s="62"/>
-      <c r="C48" s="40"/>
-      <c r="D48" s="41"/>
+      <c r="B48" s="37"/>
+      <c r="C48" s="38"/>
+      <c r="D48" s="39"/>
       <c r="E48" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="F48" s="42"/>
-      <c r="G48" s="43"/>
-      <c r="H48" s="40"/>
-      <c r="I48" s="44"/>
-      <c r="J48" s="37"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="38"/>
+      <c r="I48" s="42"/>
+      <c r="J48" s="43"/>
     </row>
     <row r="49" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B49" s="62"/>
-      <c r="C49" s="40"/>
-      <c r="D49" s="41"/>
+      <c r="B49" s="37"/>
+      <c r="C49" s="38"/>
+      <c r="D49" s="39"/>
       <c r="E49" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="F49" s="42"/>
-      <c r="G49" s="43"/>
-      <c r="H49" s="40"/>
-      <c r="I49" s="44"/>
-      <c r="J49" s="37"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="38"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="43"/>
     </row>
     <row r="50" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B50" s="62"/>
-      <c r="C50" s="40"/>
-      <c r="D50" s="41"/>
+      <c r="B50" s="37"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="39"/>
       <c r="E50" s="36" t="s">
         <v>306</v>
       </c>
-      <c r="F50" s="42"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="40"/>
-      <c r="I50" s="57"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="44"/>
       <c r="J50" s="45"/>
     </row>
     <row r="51" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B51" s="58" t="s">
+      <c r="B51" s="54" t="s">
         <v>287</v>
       </c>
-      <c r="C51" s="61" t="s">
+      <c r="C51" s="53" t="s">
         <v>167</v>
       </c>
-      <c r="D51" s="48" t="s">
+      <c r="D51" s="47" t="s">
         <v>175</v>
       </c>
       <c r="E51" s="29" t="s">
         <v>289</v>
       </c>
-      <c r="F51" s="48" t="s">
+      <c r="F51" s="47" t="s">
         <v>192</v>
       </c>
-      <c r="G51" s="48">
+      <c r="G51" s="47">
         <v>3</v>
       </c>
-      <c r="H51" s="48" t="s">
+      <c r="H51" s="47" t="s">
         <v>276</v>
       </c>
-      <c r="I51" s="51" t="s">
+      <c r="I51" s="50" t="s">
         <v>305</v>
       </c>
-      <c r="J51" s="52" t="s">
+      <c r="J51" s="51" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="52" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B52" s="38"/>
-      <c r="C52" s="60"/>
-      <c r="D52" s="41"/>
+      <c r="B52" s="55"/>
+      <c r="C52" s="52"/>
+      <c r="D52" s="39"/>
       <c r="E52" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
-      <c r="H52" s="41"/>
-      <c r="I52" s="44"/>
-      <c r="J52" s="37"/>
+      <c r="F52" s="39"/>
+      <c r="G52" s="39"/>
+      <c r="H52" s="39"/>
+      <c r="I52" s="42"/>
+      <c r="J52" s="43"/>
     </row>
     <row r="53" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B53" s="38"/>
-      <c r="C53" s="60"/>
-      <c r="D53" s="41"/>
+      <c r="B53" s="55"/>
+      <c r="C53" s="52"/>
+      <c r="D53" s="39"/>
       <c r="E53" s="27" t="s">
         <v>293</v>
       </c>
@@ -5533,54 +5533,54 @@
       <c r="G53" s="31" t="b">
         <v>1</v>
       </c>
-      <c r="H53" s="41"/>
-      <c r="I53" s="44"/>
-      <c r="J53" s="37"/>
+      <c r="H53" s="39"/>
+      <c r="I53" s="42"/>
+      <c r="J53" s="43"/>
     </row>
     <row r="54" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B54" s="59"/>
-      <c r="C54" s="60" t="s">
+      <c r="B54" s="56"/>
+      <c r="C54" s="52" t="s">
         <v>168</v>
       </c>
-      <c r="D54" s="41" t="s">
+      <c r="D54" s="39" t="s">
         <v>179</v>
       </c>
       <c r="E54" s="25" t="s">
         <v>289</v>
       </c>
-      <c r="F54" s="41" t="s">
+      <c r="F54" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="G54" s="41">
+      <c r="G54" s="39">
         <v>3</v>
       </c>
-      <c r="H54" s="41" t="s">
+      <c r="H54" s="39" t="s">
         <v>275</v>
       </c>
-      <c r="I54" s="44" t="s">
+      <c r="I54" s="42" t="s">
         <v>304</v>
       </c>
-      <c r="J54" s="37" t="s">
+      <c r="J54" s="43" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="55" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B55" s="59"/>
-      <c r="C55" s="60"/>
-      <c r="D55" s="41"/>
+      <c r="B55" s="56"/>
+      <c r="C55" s="52"/>
+      <c r="D55" s="39"/>
       <c r="E55" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="F55" s="41"/>
-      <c r="G55" s="41"/>
-      <c r="H55" s="41"/>
-      <c r="I55" s="44"/>
-      <c r="J55" s="37"/>
+      <c r="F55" s="39"/>
+      <c r="G55" s="39"/>
+      <c r="H55" s="39"/>
+      <c r="I55" s="42"/>
+      <c r="J55" s="43"/>
     </row>
     <row r="56" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B56" s="59"/>
-      <c r="C56" s="60"/>
-      <c r="D56" s="41"/>
+      <c r="B56" s="56"/>
+      <c r="C56" s="52"/>
+      <c r="D56" s="39"/>
       <c r="E56" s="27" t="s">
         <v>293</v>
       </c>
@@ -5590,54 +5590,54 @@
       <c r="G56" s="27" t="b">
         <v>1</v>
       </c>
-      <c r="H56" s="41"/>
-      <c r="I56" s="44"/>
-      <c r="J56" s="37"/>
+      <c r="H56" s="39"/>
+      <c r="I56" s="42"/>
+      <c r="J56" s="43"/>
     </row>
     <row r="57" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B57" s="38"/>
-      <c r="C57" s="40" t="s">
+      <c r="B57" s="55"/>
+      <c r="C57" s="38" t="s">
         <v>169</v>
       </c>
-      <c r="D57" s="41" t="s">
+      <c r="D57" s="39" t="s">
         <v>177</v>
       </c>
       <c r="E57" s="25" t="s">
         <v>289</v>
       </c>
-      <c r="F57" s="41" t="s">
+      <c r="F57" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="G57" s="41">
+      <c r="G57" s="39">
         <v>3</v>
       </c>
-      <c r="H57" s="41" t="s">
+      <c r="H57" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="I57" s="44" t="s">
+      <c r="I57" s="42" t="s">
         <v>304</v>
       </c>
-      <c r="J57" s="37" t="s">
+      <c r="J57" s="43" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="58" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B58" s="38"/>
-      <c r="C58" s="40"/>
-      <c r="D58" s="41"/>
+      <c r="B58" s="55"/>
+      <c r="C58" s="38"/>
+      <c r="D58" s="39"/>
       <c r="E58" s="27" t="s">
         <v>286</v>
       </c>
-      <c r="F58" s="41"/>
-      <c r="G58" s="41"/>
-      <c r="H58" s="41"/>
-      <c r="I58" s="44"/>
-      <c r="J58" s="37"/>
+      <c r="F58" s="39"/>
+      <c r="G58" s="39"/>
+      <c r="H58" s="39"/>
+      <c r="I58" s="42"/>
+      <c r="J58" s="43"/>
     </row>
     <row r="59" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B59" s="39"/>
-      <c r="C59" s="53"/>
-      <c r="D59" s="56"/>
+      <c r="B59" s="57"/>
+      <c r="C59" s="58"/>
+      <c r="D59" s="61"/>
       <c r="E59" s="28" t="s">
         <v>293</v>
       </c>
@@ -5647,12 +5647,90 @@
       <c r="G59" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="H59" s="56"/>
-      <c r="I59" s="57"/>
+      <c r="H59" s="61"/>
+      <c r="I59" s="44"/>
       <c r="J59" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="102">
+    <mergeCell ref="J3:J6"/>
+    <mergeCell ref="B3:B18"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="F3:F6"/>
+    <mergeCell ref="G3:G6"/>
+    <mergeCell ref="H3:H6"/>
+    <mergeCell ref="I3:I6"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="F11:F14"/>
+    <mergeCell ref="G11:G14"/>
+    <mergeCell ref="H11:H14"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="D7:D10"/>
+    <mergeCell ref="F7:F10"/>
+    <mergeCell ref="G7:G10"/>
+    <mergeCell ref="H7:H10"/>
+    <mergeCell ref="I7:I10"/>
+    <mergeCell ref="J23:J26"/>
+    <mergeCell ref="C23:C26"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G23:G26"/>
+    <mergeCell ref="H23:H26"/>
+    <mergeCell ref="I23:I26"/>
+    <mergeCell ref="J15:J18"/>
+    <mergeCell ref="B19:B30"/>
+    <mergeCell ref="C19:C22"/>
+    <mergeCell ref="D19:D22"/>
+    <mergeCell ref="F19:F22"/>
+    <mergeCell ref="G19:G22"/>
+    <mergeCell ref="H19:H22"/>
+    <mergeCell ref="I19:I22"/>
+    <mergeCell ref="J19:J22"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="D15:D18"/>
+    <mergeCell ref="F15:F18"/>
+    <mergeCell ref="G15:G18"/>
+    <mergeCell ref="H15:H18"/>
+    <mergeCell ref="I15:I18"/>
+    <mergeCell ref="B51:B59"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="J27:J30"/>
+    <mergeCell ref="C27:C30"/>
+    <mergeCell ref="D27:D30"/>
+    <mergeCell ref="F27:F30"/>
+    <mergeCell ref="G27:G30"/>
+    <mergeCell ref="H27:H30"/>
+    <mergeCell ref="I27:I30"/>
+    <mergeCell ref="I57:I59"/>
+    <mergeCell ref="J57:J59"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="D57:D59"/>
+    <mergeCell ref="F57:F58"/>
+    <mergeCell ref="G57:G58"/>
+    <mergeCell ref="H57:H59"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="H54:H56"/>
+    <mergeCell ref="F36:F41"/>
+    <mergeCell ref="G36:G41"/>
+    <mergeCell ref="H36:H41"/>
+    <mergeCell ref="I36:I41"/>
+    <mergeCell ref="J36:J41"/>
+    <mergeCell ref="C54:C56"/>
+    <mergeCell ref="D54:D56"/>
+    <mergeCell ref="I54:I56"/>
+    <mergeCell ref="J54:J56"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="I51:I53"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="H51:H53"/>
+    <mergeCell ref="J51:J53"/>
     <mergeCell ref="B31:B50"/>
     <mergeCell ref="C42:C46"/>
     <mergeCell ref="D42:D46"/>
@@ -5677,84 +5755,6 @@
     <mergeCell ref="J31:J35"/>
     <mergeCell ref="C36:C41"/>
     <mergeCell ref="D36:D41"/>
-    <mergeCell ref="C54:C56"/>
-    <mergeCell ref="D54:D56"/>
-    <mergeCell ref="I54:I56"/>
-    <mergeCell ref="J54:J56"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="I51:I53"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="H51:H53"/>
-    <mergeCell ref="J51:J53"/>
-    <mergeCell ref="B51:B59"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="J27:J30"/>
-    <mergeCell ref="C27:C30"/>
-    <mergeCell ref="D27:D30"/>
-    <mergeCell ref="F27:F30"/>
-    <mergeCell ref="G27:G30"/>
-    <mergeCell ref="H27:H30"/>
-    <mergeCell ref="I27:I30"/>
-    <mergeCell ref="I57:I59"/>
-    <mergeCell ref="J57:J59"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="D57:D59"/>
-    <mergeCell ref="F57:F58"/>
-    <mergeCell ref="G57:G58"/>
-    <mergeCell ref="H57:H59"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="H54:H56"/>
-    <mergeCell ref="F36:F41"/>
-    <mergeCell ref="G36:G41"/>
-    <mergeCell ref="H36:H41"/>
-    <mergeCell ref="I36:I41"/>
-    <mergeCell ref="J36:J41"/>
-    <mergeCell ref="J23:J26"/>
-    <mergeCell ref="C23:C26"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="G23:G26"/>
-    <mergeCell ref="H23:H26"/>
-    <mergeCell ref="I23:I26"/>
-    <mergeCell ref="J15:J18"/>
-    <mergeCell ref="B19:B30"/>
-    <mergeCell ref="C19:C22"/>
-    <mergeCell ref="D19:D22"/>
-    <mergeCell ref="F19:F22"/>
-    <mergeCell ref="G19:G22"/>
-    <mergeCell ref="H19:H22"/>
-    <mergeCell ref="I19:I22"/>
-    <mergeCell ref="J19:J22"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="D15:D18"/>
-    <mergeCell ref="F15:F18"/>
-    <mergeCell ref="G15:G18"/>
-    <mergeCell ref="H15:H18"/>
-    <mergeCell ref="I15:I18"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="B3:B18"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="F3:F6"/>
-    <mergeCell ref="G3:G6"/>
-    <mergeCell ref="H3:H6"/>
-    <mergeCell ref="I3:I6"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="F11:F14"/>
-    <mergeCell ref="G11:G14"/>
-    <mergeCell ref="H11:H14"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="D7:D10"/>
-    <mergeCell ref="F7:F10"/>
-    <mergeCell ref="G7:G10"/>
-    <mergeCell ref="H7:H10"/>
-    <mergeCell ref="I7:I10"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5807,1636 +5807,1636 @@
       </c>
     </row>
     <row r="3" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B3" s="63" t="s">
+      <c r="B3" s="67" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="64" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="47" t="s">
         <v>142</v>
       </c>
       <c r="E3" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="F3" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G3" s="43">
+      <c r="G3" s="41">
         <v>4</v>
       </c>
-      <c r="H3" s="47" t="s">
+      <c r="H3" s="46" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="I3" s="50" t="s">
         <v>268</v>
       </c>
-      <c r="J3" s="52" t="s">
+      <c r="J3" s="51" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B4" s="64"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="41"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="39"/>
       <c r="E4" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="37"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="43"/>
     </row>
     <row r="5" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B5" s="64"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="41"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="39"/>
       <c r="E5" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="F5" s="42"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="37"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
     </row>
     <row r="6" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B6" s="64"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="41"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="39"/>
       <c r="E6" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="37"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="43"/>
     </row>
     <row r="7" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B7" s="64"/>
-      <c r="C7" s="66" t="s">
+      <c r="B7" s="68"/>
+      <c r="C7" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="39" t="s">
         <v>143</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="F7" s="42" t="s">
+      <c r="F7" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G7" s="43">
+      <c r="G7" s="41">
         <v>2</v>
       </c>
-      <c r="H7" s="40" t="s">
+      <c r="H7" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="I7" s="44" t="s">
+      <c r="I7" s="42" t="s">
         <v>267</v>
       </c>
-      <c r="J7" s="37" t="s">
+      <c r="J7" s="43" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B8" s="64"/>
-      <c r="C8" s="66"/>
-      <c r="D8" s="41"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="39"/>
       <c r="E8" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="37"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="43"/>
     </row>
     <row r="9" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B9" s="64"/>
-      <c r="C9" s="66"/>
-      <c r="D9" s="41"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="39"/>
       <c r="E9" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="37"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="43"/>
     </row>
     <row r="10" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B10" s="64"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="41"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="39"/>
       <c r="E10" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="F10" s="42"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="37"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="43"/>
     </row>
     <row r="11" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B11" s="64"/>
-      <c r="C11" s="66" t="s">
+      <c r="B11" s="68"/>
+      <c r="C11" s="65" t="s">
         <v>127</v>
       </c>
-      <c r="D11" s="41" t="s">
+      <c r="D11" s="39" t="s">
         <v>135</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="F11" s="42" t="s">
+      <c r="F11" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G11" s="43">
+      <c r="G11" s="41">
         <v>2</v>
       </c>
-      <c r="H11" s="40" t="s">
+      <c r="H11" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="I11" s="44" t="s">
+      <c r="I11" s="42" t="s">
         <v>266</v>
       </c>
-      <c r="J11" s="37" t="s">
+      <c r="J11" s="43" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B12" s="64"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="41"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="39"/>
       <c r="E12" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="F12" s="42"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="37"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="43"/>
     </row>
     <row r="13" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B13" s="64"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="41"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="39"/>
       <c r="E13" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="F13" s="42"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="37"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="43"/>
     </row>
     <row r="14" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B14" s="65"/>
-      <c r="C14" s="68"/>
-      <c r="D14" s="56"/>
+      <c r="B14" s="69"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="61"/>
       <c r="E14" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="F14" s="54"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="57"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="44"/>
       <c r="J14" s="45"/>
     </row>
     <row r="15" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B15" s="46" t="s">
+      <c r="B15" s="62" t="s">
         <v>140</v>
       </c>
-      <c r="C15" s="47" t="s">
+      <c r="C15" s="46" t="s">
         <v>113</v>
       </c>
-      <c r="D15" s="48" t="s">
+      <c r="D15" s="47" t="s">
         <v>145</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="F15" s="49" t="s">
+      <c r="F15" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="G15" s="50">
+      <c r="G15" s="49">
         <v>4</v>
       </c>
-      <c r="H15" s="48" t="s">
+      <c r="H15" s="47" t="s">
         <v>131</v>
       </c>
-      <c r="I15" s="51" t="s">
+      <c r="I15" s="50" t="s">
         <v>242</v>
       </c>
-      <c r="J15" s="52" t="s">
+      <c r="J15" s="51" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B16" s="38"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
       <c r="E16" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="F16" s="42"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="37"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="43"/>
     </row>
     <row r="17" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B17" s="38"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
       <c r="E17" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="F17" s="42"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="37"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="43"/>
     </row>
     <row r="18" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B18" s="38"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
       <c r="E18" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="F18" s="42"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="37"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="43"/>
     </row>
     <row r="19" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B19" s="38"/>
-      <c r="C19" s="40" t="s">
+      <c r="B19" s="55"/>
+      <c r="C19" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="D19" s="41" t="s">
+      <c r="D19" s="39" t="s">
         <v>146</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="F19" s="42" t="s">
+      <c r="F19" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G19" s="43">
+      <c r="G19" s="41">
         <v>4</v>
       </c>
-      <c r="H19" s="41" t="s">
+      <c r="H19" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="I19" s="44" t="s">
+      <c r="I19" s="42" t="s">
         <v>242</v>
       </c>
-      <c r="J19" s="37" t="s">
+      <c r="J19" s="43" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="20" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B20" s="38"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="41"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="39"/>
       <c r="E20" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="F20" s="42"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="37"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="43"/>
     </row>
     <row r="21" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B21" s="38"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
       <c r="E21" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="F21" s="42"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="37"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="43"/>
     </row>
     <row r="22" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B22" s="38"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
       <c r="E22" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="F22" s="42"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="37"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="43"/>
     </row>
     <row r="23" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B23" s="38"/>
-      <c r="C23" s="40" t="s">
+      <c r="B23" s="55"/>
+      <c r="C23" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="D23" s="40" t="s">
+      <c r="D23" s="38" t="s">
         <v>144</v>
       </c>
       <c r="E23" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="F23" s="42" t="s">
+      <c r="F23" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G23" s="43">
+      <c r="G23" s="41">
         <v>4</v>
       </c>
-      <c r="H23" s="41" t="s">
+      <c r="H23" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="I23" s="44" t="s">
+      <c r="I23" s="42" t="s">
         <v>255</v>
       </c>
-      <c r="J23" s="37" t="s">
+      <c r="J23" s="43" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="24" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B24" s="38"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
       <c r="E24" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="F24" s="42"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="37"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="43"/>
     </row>
     <row r="25" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B25" s="38"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
       <c r="E25" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="F25" s="42"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="44"/>
-      <c r="J25" s="37"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="43"/>
     </row>
     <row r="26" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B26" s="38"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
+      <c r="B26" s="55"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
       <c r="E26" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="F26" s="42"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="44"/>
-      <c r="J26" s="37"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="43"/>
     </row>
     <row r="27" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B27" s="38"/>
-      <c r="C27" s="40" t="s">
+      <c r="B27" s="55"/>
+      <c r="C27" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="D27" s="40" t="s">
+      <c r="D27" s="38" t="s">
         <v>153</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="F27" s="42" t="s">
+      <c r="F27" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G27" s="43">
+      <c r="G27" s="41">
         <v>4</v>
       </c>
-      <c r="H27" s="41" t="s">
+      <c r="H27" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="I27" s="44" t="s">
+      <c r="I27" s="42" t="s">
         <v>243</v>
       </c>
-      <c r="J27" s="37" t="s">
+      <c r="J27" s="43" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="28" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B28" s="38"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
       <c r="E28" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="F28" s="42"/>
-      <c r="G28" s="43"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="37"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="43"/>
     </row>
     <row r="29" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B29" s="38"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
+      <c r="B29" s="55"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
       <c r="E29" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="F29" s="42"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="37"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="43"/>
     </row>
     <row r="30" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B30" s="38"/>
-      <c r="C30" s="40"/>
-      <c r="D30" s="40"/>
+      <c r="B30" s="55"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
       <c r="E30" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="F30" s="42"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="37"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="43"/>
     </row>
     <row r="31" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B31" s="38"/>
-      <c r="C31" s="40" t="s">
+      <c r="B31" s="55"/>
+      <c r="C31" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="40" t="s">
+      <c r="D31" s="38" t="s">
         <v>154</v>
       </c>
       <c r="E31" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="F31" s="42" t="s">
+      <c r="F31" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G31" s="43">
+      <c r="G31" s="41">
         <v>4</v>
       </c>
-      <c r="H31" s="41" t="s">
+      <c r="H31" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="I31" s="44" t="s">
+      <c r="I31" s="42" t="s">
         <v>244</v>
       </c>
-      <c r="J31" s="37" t="s">
+      <c r="J31" s="43" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="32" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B32" s="38"/>
-      <c r="C32" s="40"/>
-      <c r="D32" s="40"/>
+      <c r="B32" s="55"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
       <c r="E32" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="F32" s="42"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="41"/>
-      <c r="I32" s="44"/>
-      <c r="J32" s="37"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="43"/>
     </row>
     <row r="33" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B33" s="38"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="40"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38"/>
       <c r="E33" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="F33" s="42"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="44"/>
-      <c r="J33" s="37"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="43"/>
     </row>
     <row r="34" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B34" s="39"/>
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
+      <c r="B34" s="57"/>
+      <c r="C34" s="58"/>
+      <c r="D34" s="58"/>
       <c r="E34" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="F34" s="54"/>
-      <c r="G34" s="55"/>
-      <c r="H34" s="56"/>
-      <c r="I34" s="57"/>
+      <c r="F34" s="59"/>
+      <c r="G34" s="60"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="44"/>
       <c r="J34" s="45"/>
     </row>
     <row r="35" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B35" s="46" t="s">
+      <c r="B35" s="62" t="s">
         <v>141</v>
       </c>
-      <c r="C35" s="47" t="s">
+      <c r="C35" s="46" t="s">
         <v>115</v>
       </c>
-      <c r="D35" s="48" t="s">
+      <c r="D35" s="47" t="s">
         <v>147</v>
       </c>
       <c r="E35" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="F35" s="49" t="s">
+      <c r="F35" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="G35" s="50">
+      <c r="G35" s="49">
         <v>4</v>
       </c>
-      <c r="H35" s="48" t="s">
+      <c r="H35" s="47" t="s">
         <v>128</v>
       </c>
-      <c r="I35" s="51" t="s">
+      <c r="I35" s="50" t="s">
         <v>256</v>
       </c>
-      <c r="J35" s="52" t="s">
+      <c r="J35" s="51" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="36" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B36" s="38"/>
-      <c r="C36" s="40"/>
-      <c r="D36" s="41"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="39"/>
       <c r="E36" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="F36" s="42"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="41"/>
-      <c r="I36" s="44"/>
-      <c r="J36" s="37"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="43"/>
     </row>
     <row r="37" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B37" s="38"/>
-      <c r="C37" s="40"/>
-      <c r="D37" s="40"/>
+      <c r="B37" s="55"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38"/>
       <c r="E37" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="F37" s="42"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="41"/>
-      <c r="I37" s="44"/>
-      <c r="J37" s="37"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="43"/>
     </row>
     <row r="38" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B38" s="38"/>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
+      <c r="B38" s="55"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
       <c r="E38" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="F38" s="42"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="41"/>
-      <c r="I38" s="44"/>
-      <c r="J38" s="37"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="43"/>
     </row>
     <row r="39" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B39" s="38"/>
-      <c r="C39" s="40" t="s">
+      <c r="B39" s="55"/>
+      <c r="C39" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="D39" s="41" t="s">
+      <c r="D39" s="39" t="s">
         <v>148</v>
       </c>
       <c r="E39" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="F39" s="42" t="s">
+      <c r="F39" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G39" s="43">
+      <c r="G39" s="41">
         <v>4</v>
       </c>
-      <c r="H39" s="41" t="s">
+      <c r="H39" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="I39" s="44" t="s">
+      <c r="I39" s="42" t="s">
         <v>256</v>
       </c>
-      <c r="J39" s="37" t="s">
+      <c r="J39" s="43" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="40" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B40" s="38"/>
-      <c r="C40" s="40"/>
-      <c r="D40" s="41"/>
+      <c r="B40" s="55"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="39"/>
       <c r="E40" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="F40" s="42"/>
-      <c r="G40" s="43"/>
-      <c r="H40" s="41"/>
-      <c r="I40" s="44"/>
-      <c r="J40" s="37"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="41"/>
+      <c r="H40" s="39"/>
+      <c r="I40" s="42"/>
+      <c r="J40" s="43"/>
     </row>
     <row r="41" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B41" s="38"/>
-      <c r="C41" s="40"/>
-      <c r="D41" s="40"/>
+      <c r="B41" s="55"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="38"/>
       <c r="E41" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="F41" s="42"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="41"/>
-      <c r="I41" s="44"/>
-      <c r="J41" s="37"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="39"/>
+      <c r="I41" s="42"/>
+      <c r="J41" s="43"/>
     </row>
     <row r="42" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B42" s="38"/>
-      <c r="C42" s="40"/>
-      <c r="D42" s="40"/>
+      <c r="B42" s="55"/>
+      <c r="C42" s="38"/>
+      <c r="D42" s="38"/>
       <c r="E42" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="F42" s="42"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="41"/>
-      <c r="I42" s="44"/>
-      <c r="J42" s="37"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="41"/>
+      <c r="H42" s="39"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="43"/>
     </row>
     <row r="43" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B43" s="38"/>
-      <c r="C43" s="40" t="s">
+      <c r="B43" s="55"/>
+      <c r="C43" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="D43" s="41" t="s">
+      <c r="D43" s="39" t="s">
         <v>149</v>
       </c>
       <c r="E43" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="F43" s="42" t="s">
+      <c r="F43" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G43" s="43">
+      <c r="G43" s="41">
         <v>4</v>
       </c>
-      <c r="H43" s="41" t="s">
+      <c r="H43" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="I43" s="44" t="s">
+      <c r="I43" s="42" t="s">
         <v>258</v>
       </c>
-      <c r="J43" s="37" t="s">
+      <c r="J43" s="43" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="44" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B44" s="38"/>
-      <c r="C44" s="40"/>
-      <c r="D44" s="41"/>
+      <c r="B44" s="55"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="39"/>
       <c r="E44" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="F44" s="42"/>
-      <c r="G44" s="43"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="44"/>
-      <c r="J44" s="37"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="39"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="43"/>
     </row>
     <row r="45" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B45" s="38"/>
-      <c r="C45" s="40"/>
-      <c r="D45" s="40"/>
+      <c r="B45" s="55"/>
+      <c r="C45" s="38"/>
+      <c r="D45" s="38"/>
       <c r="E45" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="F45" s="42"/>
-      <c r="G45" s="43"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="44"/>
-      <c r="J45" s="37"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="39"/>
+      <c r="I45" s="42"/>
+      <c r="J45" s="43"/>
     </row>
     <row r="46" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B46" s="38"/>
-      <c r="C46" s="40"/>
-      <c r="D46" s="40"/>
+      <c r="B46" s="55"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="38"/>
       <c r="E46" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="F46" s="42"/>
-      <c r="G46" s="43"/>
-      <c r="H46" s="41"/>
-      <c r="I46" s="44"/>
-      <c r="J46" s="37"/>
+      <c r="F46" s="40"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="39"/>
+      <c r="I46" s="42"/>
+      <c r="J46" s="43"/>
     </row>
     <row r="47" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B47" s="38"/>
-      <c r="C47" s="40" t="s">
+      <c r="B47" s="55"/>
+      <c r="C47" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="D47" s="41" t="s">
+      <c r="D47" s="39" t="s">
         <v>150</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="F47" s="42" t="s">
+      <c r="F47" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G47" s="43">
+      <c r="G47" s="41">
         <v>4</v>
       </c>
-      <c r="H47" s="41" t="s">
+      <c r="H47" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="I47" s="44" t="s">
+      <c r="I47" s="42" t="s">
         <v>245</v>
       </c>
-      <c r="J47" s="37" t="s">
+      <c r="J47" s="43" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="48" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B48" s="38"/>
-      <c r="C48" s="40"/>
-      <c r="D48" s="41"/>
+      <c r="B48" s="55"/>
+      <c r="C48" s="38"/>
+      <c r="D48" s="39"/>
       <c r="E48" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="F48" s="42"/>
-      <c r="G48" s="43"/>
-      <c r="H48" s="41"/>
-      <c r="I48" s="44"/>
-      <c r="J48" s="37"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="39"/>
+      <c r="I48" s="42"/>
+      <c r="J48" s="43"/>
     </row>
     <row r="49" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B49" s="38"/>
-      <c r="C49" s="40"/>
-      <c r="D49" s="40"/>
+      <c r="B49" s="55"/>
+      <c r="C49" s="38"/>
+      <c r="D49" s="38"/>
       <c r="E49" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="F49" s="42"/>
-      <c r="G49" s="43"/>
-      <c r="H49" s="41"/>
-      <c r="I49" s="44"/>
-      <c r="J49" s="37"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="39"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="43"/>
     </row>
     <row r="50" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B50" s="38"/>
-      <c r="C50" s="40"/>
-      <c r="D50" s="40"/>
+      <c r="B50" s="55"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
       <c r="E50" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="F50" s="42"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="41"/>
-      <c r="I50" s="44"/>
-      <c r="J50" s="37"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="39"/>
+      <c r="I50" s="42"/>
+      <c r="J50" s="43"/>
     </row>
     <row r="51" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B51" s="38"/>
-      <c r="C51" s="40" t="s">
+      <c r="B51" s="55"/>
+      <c r="C51" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="D51" s="41" t="s">
+      <c r="D51" s="39" t="s">
         <v>151</v>
       </c>
       <c r="E51" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="F51" s="42" t="s">
+      <c r="F51" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G51" s="43">
+      <c r="G51" s="41">
         <v>4</v>
       </c>
-      <c r="H51" s="41" t="s">
+      <c r="H51" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="I51" s="44" t="s">
+      <c r="I51" s="42" t="s">
         <v>256</v>
       </c>
-      <c r="J51" s="37" t="s">
+      <c r="J51" s="43" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="52" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B52" s="38"/>
-      <c r="C52" s="40"/>
-      <c r="D52" s="41"/>
+      <c r="B52" s="55"/>
+      <c r="C52" s="38"/>
+      <c r="D52" s="39"/>
       <c r="E52" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="F52" s="42"/>
-      <c r="G52" s="43"/>
-      <c r="H52" s="41"/>
-      <c r="I52" s="44"/>
-      <c r="J52" s="37"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="41"/>
+      <c r="H52" s="39"/>
+      <c r="I52" s="42"/>
+      <c r="J52" s="43"/>
     </row>
     <row r="53" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B53" s="38"/>
-      <c r="C53" s="40"/>
-      <c r="D53" s="40"/>
+      <c r="B53" s="55"/>
+      <c r="C53" s="38"/>
+      <c r="D53" s="38"/>
       <c r="E53" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="F53" s="42"/>
-      <c r="G53" s="43"/>
-      <c r="H53" s="41"/>
-      <c r="I53" s="44"/>
-      <c r="J53" s="37"/>
+      <c r="F53" s="40"/>
+      <c r="G53" s="41"/>
+      <c r="H53" s="39"/>
+      <c r="I53" s="42"/>
+      <c r="J53" s="43"/>
     </row>
     <row r="54" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B54" s="38"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="40"/>
+      <c r="B54" s="55"/>
+      <c r="C54" s="38"/>
+      <c r="D54" s="38"/>
       <c r="E54" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="F54" s="42"/>
-      <c r="G54" s="43"/>
-      <c r="H54" s="41"/>
-      <c r="I54" s="44"/>
-      <c r="J54" s="37"/>
+      <c r="F54" s="40"/>
+      <c r="G54" s="41"/>
+      <c r="H54" s="39"/>
+      <c r="I54" s="42"/>
+      <c r="J54" s="43"/>
     </row>
     <row r="55" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B55" s="38"/>
-      <c r="C55" s="40" t="s">
+      <c r="B55" s="55"/>
+      <c r="C55" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="D55" s="41" t="s">
+      <c r="D55" s="39" t="s">
         <v>152</v>
       </c>
       <c r="E55" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="F55" s="42" t="s">
+      <c r="F55" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G55" s="43">
+      <c r="G55" s="41">
         <v>4</v>
       </c>
-      <c r="H55" s="41" t="s">
+      <c r="H55" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="I55" s="44" t="s">
+      <c r="I55" s="42" t="s">
         <v>258</v>
       </c>
-      <c r="J55" s="37" t="s">
+      <c r="J55" s="43" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="56" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B56" s="38"/>
-      <c r="C56" s="40"/>
-      <c r="D56" s="41"/>
+      <c r="B56" s="55"/>
+      <c r="C56" s="38"/>
+      <c r="D56" s="39"/>
       <c r="E56" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="F56" s="42"/>
-      <c r="G56" s="43"/>
-      <c r="H56" s="41"/>
-      <c r="I56" s="44"/>
-      <c r="J56" s="37"/>
+      <c r="F56" s="40"/>
+      <c r="G56" s="41"/>
+      <c r="H56" s="39"/>
+      <c r="I56" s="42"/>
+      <c r="J56" s="43"/>
     </row>
     <row r="57" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B57" s="38"/>
-      <c r="C57" s="40"/>
-      <c r="D57" s="40"/>
+      <c r="B57" s="55"/>
+      <c r="C57" s="38"/>
+      <c r="D57" s="38"/>
       <c r="E57" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="F57" s="42"/>
-      <c r="G57" s="43"/>
-      <c r="H57" s="41"/>
-      <c r="I57" s="44"/>
-      <c r="J57" s="37"/>
+      <c r="F57" s="40"/>
+      <c r="G57" s="41"/>
+      <c r="H57" s="39"/>
+      <c r="I57" s="42"/>
+      <c r="J57" s="43"/>
     </row>
     <row r="58" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B58" s="38"/>
-      <c r="C58" s="40"/>
-      <c r="D58" s="40"/>
+      <c r="B58" s="55"/>
+      <c r="C58" s="38"/>
+      <c r="D58" s="38"/>
       <c r="E58" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="F58" s="42"/>
-      <c r="G58" s="43"/>
-      <c r="H58" s="41"/>
-      <c r="I58" s="44"/>
-      <c r="J58" s="37"/>
+      <c r="F58" s="40"/>
+      <c r="G58" s="41"/>
+      <c r="H58" s="39"/>
+      <c r="I58" s="42"/>
+      <c r="J58" s="43"/>
     </row>
     <row r="59" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B59" s="38"/>
-      <c r="C59" s="40" t="s">
+      <c r="B59" s="55"/>
+      <c r="C59" s="38" t="s">
         <v>155</v>
       </c>
-      <c r="D59" s="40" t="s">
+      <c r="D59" s="38" t="s">
         <v>122</v>
       </c>
       <c r="E59" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="F59" s="42" t="s">
+      <c r="F59" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G59" s="43">
+      <c r="G59" s="41">
         <v>4</v>
       </c>
-      <c r="H59" s="41" t="s">
+      <c r="H59" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="I59" s="44" t="s">
+      <c r="I59" s="42" t="s">
         <v>257</v>
       </c>
-      <c r="J59" s="37" t="s">
+      <c r="J59" s="43" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="60" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B60" s="38"/>
-      <c r="C60" s="40"/>
-      <c r="D60" s="40"/>
+      <c r="B60" s="55"/>
+      <c r="C60" s="38"/>
+      <c r="D60" s="38"/>
       <c r="E60" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="F60" s="42"/>
-      <c r="G60" s="43"/>
-      <c r="H60" s="41"/>
-      <c r="I60" s="44"/>
-      <c r="J60" s="37"/>
+      <c r="F60" s="40"/>
+      <c r="G60" s="41"/>
+      <c r="H60" s="39"/>
+      <c r="I60" s="42"/>
+      <c r="J60" s="43"/>
     </row>
     <row r="61" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B61" s="38"/>
-      <c r="C61" s="40"/>
-      <c r="D61" s="40"/>
+      <c r="B61" s="55"/>
+      <c r="C61" s="38"/>
+      <c r="D61" s="38"/>
       <c r="E61" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="F61" s="42"/>
-      <c r="G61" s="43"/>
-      <c r="H61" s="41"/>
-      <c r="I61" s="44"/>
-      <c r="J61" s="37"/>
+      <c r="F61" s="40"/>
+      <c r="G61" s="41"/>
+      <c r="H61" s="39"/>
+      <c r="I61" s="42"/>
+      <c r="J61" s="43"/>
     </row>
     <row r="62" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B62" s="39"/>
-      <c r="C62" s="53"/>
-      <c r="D62" s="53"/>
+      <c r="B62" s="57"/>
+      <c r="C62" s="58"/>
+      <c r="D62" s="58"/>
       <c r="E62" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="F62" s="54"/>
-      <c r="G62" s="55"/>
-      <c r="H62" s="56"/>
-      <c r="I62" s="57"/>
+      <c r="F62" s="59"/>
+      <c r="G62" s="60"/>
+      <c r="H62" s="61"/>
+      <c r="I62" s="44"/>
       <c r="J62" s="45"/>
     </row>
     <row r="63" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B63" s="58" t="s">
+      <c r="B63" s="54" t="s">
         <v>216</v>
       </c>
-      <c r="C63" s="47" t="s">
+      <c r="C63" s="46" t="s">
         <v>162</v>
       </c>
-      <c r="D63" s="48" t="s">
+      <c r="D63" s="47" t="s">
         <v>172</v>
       </c>
       <c r="E63" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="F63" s="42" t="s">
+      <c r="F63" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G63" s="43">
+      <c r="G63" s="41">
         <v>3</v>
       </c>
-      <c r="H63" s="47"/>
-      <c r="I63" s="51" t="s">
+      <c r="H63" s="46"/>
+      <c r="I63" s="50" t="s">
         <v>262</v>
       </c>
-      <c r="J63" s="52" t="s">
+      <c r="J63" s="51" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="64" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B64" s="38"/>
-      <c r="C64" s="40"/>
-      <c r="D64" s="41"/>
+      <c r="B64" s="55"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="39"/>
       <c r="E64" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="F64" s="42"/>
-      <c r="G64" s="43"/>
-      <c r="H64" s="40"/>
-      <c r="I64" s="44"/>
-      <c r="J64" s="37"/>
+      <c r="F64" s="40"/>
+      <c r="G64" s="41"/>
+      <c r="H64" s="38"/>
+      <c r="I64" s="42"/>
+      <c r="J64" s="43"/>
     </row>
     <row r="65" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B65" s="38"/>
-      <c r="C65" s="40"/>
-      <c r="D65" s="41"/>
+      <c r="B65" s="55"/>
+      <c r="C65" s="38"/>
+      <c r="D65" s="39"/>
       <c r="E65" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="F65" s="42"/>
-      <c r="G65" s="43"/>
-      <c r="H65" s="40"/>
-      <c r="I65" s="44"/>
-      <c r="J65" s="37"/>
+      <c r="F65" s="40"/>
+      <c r="G65" s="41"/>
+      <c r="H65" s="38"/>
+      <c r="I65" s="42"/>
+      <c r="J65" s="43"/>
     </row>
     <row r="66" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B66" s="38"/>
-      <c r="C66" s="40"/>
-      <c r="D66" s="41"/>
+      <c r="B66" s="55"/>
+      <c r="C66" s="38"/>
+      <c r="D66" s="39"/>
       <c r="E66" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="F66" s="42"/>
-      <c r="G66" s="43"/>
-      <c r="H66" s="40"/>
-      <c r="I66" s="44"/>
-      <c r="J66" s="37"/>
+      <c r="F66" s="40"/>
+      <c r="G66" s="41"/>
+      <c r="H66" s="38"/>
+      <c r="I66" s="42"/>
+      <c r="J66" s="43"/>
     </row>
     <row r="67" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B67" s="38"/>
-      <c r="C67" s="40" t="s">
+      <c r="B67" s="55"/>
+      <c r="C67" s="38" t="s">
         <v>163</v>
       </c>
-      <c r="D67" s="41" t="s">
+      <c r="D67" s="39" t="s">
         <v>240</v>
       </c>
       <c r="E67" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="F67" s="42" t="s">
+      <c r="F67" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G67" s="43">
+      <c r="G67" s="41">
         <v>3</v>
       </c>
-      <c r="H67" s="40"/>
-      <c r="I67" s="44" t="s">
+      <c r="H67" s="38"/>
+      <c r="I67" s="42" t="s">
         <v>263</v>
       </c>
-      <c r="J67" s="37" t="s">
+      <c r="J67" s="43" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="68" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B68" s="38"/>
-      <c r="C68" s="40"/>
-      <c r="D68" s="41"/>
+      <c r="B68" s="55"/>
+      <c r="C68" s="38"/>
+      <c r="D68" s="39"/>
       <c r="E68" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="F68" s="42"/>
-      <c r="G68" s="43"/>
-      <c r="H68" s="40"/>
-      <c r="I68" s="44"/>
-      <c r="J68" s="37"/>
+      <c r="F68" s="40"/>
+      <c r="G68" s="41"/>
+      <c r="H68" s="38"/>
+      <c r="I68" s="42"/>
+      <c r="J68" s="43"/>
     </row>
     <row r="69" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B69" s="38"/>
-      <c r="C69" s="40"/>
-      <c r="D69" s="41"/>
+      <c r="B69" s="55"/>
+      <c r="C69" s="38"/>
+      <c r="D69" s="39"/>
       <c r="E69" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="F69" s="42"/>
-      <c r="G69" s="43"/>
-      <c r="H69" s="40"/>
-      <c r="I69" s="44"/>
-      <c r="J69" s="37"/>
+      <c r="F69" s="40"/>
+      <c r="G69" s="41"/>
+      <c r="H69" s="38"/>
+      <c r="I69" s="42"/>
+      <c r="J69" s="43"/>
     </row>
     <row r="70" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B70" s="38"/>
-      <c r="C70" s="40"/>
-      <c r="D70" s="41"/>
+      <c r="B70" s="55"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="39"/>
       <c r="E70" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="F70" s="42"/>
-      <c r="G70" s="43"/>
-      <c r="H70" s="40"/>
-      <c r="I70" s="44"/>
-      <c r="J70" s="37"/>
+      <c r="F70" s="40"/>
+      <c r="G70" s="41"/>
+      <c r="H70" s="38"/>
+      <c r="I70" s="42"/>
+      <c r="J70" s="43"/>
     </row>
     <row r="71" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B71" s="38"/>
-      <c r="C71" s="40" t="s">
+      <c r="B71" s="55"/>
+      <c r="C71" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="D71" s="41" t="s">
+      <c r="D71" s="39" t="s">
         <v>176</v>
       </c>
       <c r="E71" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="F71" s="42" t="s">
+      <c r="F71" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G71" s="43">
+      <c r="G71" s="41">
         <v>3</v>
       </c>
-      <c r="H71" s="40"/>
-      <c r="I71" s="44" t="s">
+      <c r="H71" s="38"/>
+      <c r="I71" s="42" t="s">
         <v>263</v>
       </c>
-      <c r="J71" s="37" t="s">
+      <c r="J71" s="43" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="72" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B72" s="38"/>
-      <c r="C72" s="40"/>
-      <c r="D72" s="41"/>
+      <c r="B72" s="55"/>
+      <c r="C72" s="38"/>
+      <c r="D72" s="39"/>
       <c r="E72" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="F72" s="42"/>
-      <c r="G72" s="43"/>
-      <c r="H72" s="40"/>
-      <c r="I72" s="44"/>
-      <c r="J72" s="37"/>
+      <c r="F72" s="40"/>
+      <c r="G72" s="41"/>
+      <c r="H72" s="38"/>
+      <c r="I72" s="42"/>
+      <c r="J72" s="43"/>
     </row>
     <row r="73" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B73" s="38"/>
-      <c r="C73" s="40"/>
-      <c r="D73" s="41"/>
+      <c r="B73" s="55"/>
+      <c r="C73" s="38"/>
+      <c r="D73" s="39"/>
       <c r="E73" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="F73" s="42"/>
-      <c r="G73" s="43"/>
-      <c r="H73" s="40"/>
-      <c r="I73" s="44"/>
-      <c r="J73" s="37"/>
+      <c r="F73" s="40"/>
+      <c r="G73" s="41"/>
+      <c r="H73" s="38"/>
+      <c r="I73" s="42"/>
+      <c r="J73" s="43"/>
     </row>
     <row r="74" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B74" s="38"/>
-      <c r="C74" s="40"/>
-      <c r="D74" s="41"/>
+      <c r="B74" s="55"/>
+      <c r="C74" s="38"/>
+      <c r="D74" s="39"/>
       <c r="E74" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="F74" s="42"/>
-      <c r="G74" s="43"/>
-      <c r="H74" s="40"/>
-      <c r="I74" s="44"/>
-      <c r="J74" s="37"/>
+      <c r="F74" s="40"/>
+      <c r="G74" s="41"/>
+      <c r="H74" s="38"/>
+      <c r="I74" s="42"/>
+      <c r="J74" s="43"/>
     </row>
     <row r="75" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B75" s="38"/>
-      <c r="C75" s="60" t="s">
+      <c r="B75" s="55"/>
+      <c r="C75" s="52" t="s">
         <v>166</v>
       </c>
-      <c r="D75" s="41" t="s">
+      <c r="D75" s="39" t="s">
         <v>173</v>
       </c>
       <c r="E75" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="F75" s="42" t="s">
+      <c r="F75" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G75" s="43">
+      <c r="G75" s="41">
         <v>3</v>
       </c>
-      <c r="H75" s="40"/>
-      <c r="I75" s="44" t="s">
+      <c r="H75" s="38"/>
+      <c r="I75" s="42" t="s">
         <v>260</v>
       </c>
-      <c r="J75" s="37" t="s">
+      <c r="J75" s="43" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="76" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B76" s="38"/>
-      <c r="C76" s="60"/>
-      <c r="D76" s="41"/>
+      <c r="B76" s="55"/>
+      <c r="C76" s="52"/>
+      <c r="D76" s="39"/>
       <c r="E76" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="F76" s="42"/>
-      <c r="G76" s="43"/>
-      <c r="H76" s="40"/>
-      <c r="I76" s="44"/>
-      <c r="J76" s="37"/>
+      <c r="F76" s="40"/>
+      <c r="G76" s="41"/>
+      <c r="H76" s="38"/>
+      <c r="I76" s="42"/>
+      <c r="J76" s="43"/>
     </row>
     <row r="77" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B77" s="38"/>
-      <c r="C77" s="60"/>
-      <c r="D77" s="41"/>
+      <c r="B77" s="55"/>
+      <c r="C77" s="52"/>
+      <c r="D77" s="39"/>
       <c r="E77" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="F77" s="42"/>
-      <c r="G77" s="43"/>
-      <c r="H77" s="40"/>
-      <c r="I77" s="44"/>
-      <c r="J77" s="37"/>
+      <c r="F77" s="40"/>
+      <c r="G77" s="41"/>
+      <c r="H77" s="38"/>
+      <c r="I77" s="42"/>
+      <c r="J77" s="43"/>
     </row>
     <row r="78" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B78" s="38"/>
-      <c r="C78" s="60" t="s">
+      <c r="B78" s="55"/>
+      <c r="C78" s="52" t="s">
         <v>165</v>
       </c>
-      <c r="D78" s="41" t="s">
+      <c r="D78" s="39" t="s">
         <v>174</v>
       </c>
       <c r="E78" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="F78" s="42" t="s">
+      <c r="F78" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G78" s="43">
+      <c r="G78" s="41">
         <v>5</v>
       </c>
-      <c r="H78" s="40"/>
-      <c r="I78" s="44" t="s">
+      <c r="H78" s="38"/>
+      <c r="I78" s="42" t="s">
         <v>264</v>
       </c>
-      <c r="J78" s="37" t="s">
+      <c r="J78" s="43" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="79" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B79" s="38"/>
-      <c r="C79" s="60"/>
-      <c r="D79" s="41"/>
+      <c r="B79" s="55"/>
+      <c r="C79" s="52"/>
+      <c r="D79" s="39"/>
       <c r="E79" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="F79" s="42"/>
-      <c r="G79" s="43"/>
-      <c r="H79" s="40"/>
-      <c r="I79" s="44"/>
-      <c r="J79" s="37"/>
+      <c r="F79" s="40"/>
+      <c r="G79" s="41"/>
+      <c r="H79" s="38"/>
+      <c r="I79" s="42"/>
+      <c r="J79" s="43"/>
     </row>
     <row r="80" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B80" s="38"/>
-      <c r="C80" s="60"/>
-      <c r="D80" s="41"/>
+      <c r="B80" s="55"/>
+      <c r="C80" s="52"/>
+      <c r="D80" s="39"/>
       <c r="E80" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="F80" s="42"/>
-      <c r="G80" s="43"/>
-      <c r="H80" s="40"/>
-      <c r="I80" s="44"/>
-      <c r="J80" s="37"/>
+      <c r="F80" s="40"/>
+      <c r="G80" s="41"/>
+      <c r="H80" s="38"/>
+      <c r="I80" s="42"/>
+      <c r="J80" s="43"/>
     </row>
     <row r="81" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B81" s="38"/>
-      <c r="C81" s="60"/>
-      <c r="D81" s="41"/>
+      <c r="B81" s="55"/>
+      <c r="C81" s="52"/>
+      <c r="D81" s="39"/>
       <c r="E81" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="F81" s="42"/>
-      <c r="G81" s="43"/>
-      <c r="H81" s="40"/>
-      <c r="I81" s="44"/>
-      <c r="J81" s="37"/>
+      <c r="F81" s="40"/>
+      <c r="G81" s="41"/>
+      <c r="H81" s="38"/>
+      <c r="I81" s="42"/>
+      <c r="J81" s="43"/>
     </row>
     <row r="82" spans="2:10" ht="25.05" customHeight="1">
       <c r="B82" s="24"/>
-      <c r="C82" s="60"/>
-      <c r="D82" s="41"/>
+      <c r="C82" s="52"/>
+      <c r="D82" s="39"/>
       <c r="E82" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="F82" s="42"/>
-      <c r="G82" s="43"/>
-      <c r="H82" s="40"/>
-      <c r="I82" s="44"/>
-      <c r="J82" s="37"/>
+      <c r="F82" s="40"/>
+      <c r="G82" s="41"/>
+      <c r="H82" s="38"/>
+      <c r="I82" s="42"/>
+      <c r="J82" s="43"/>
     </row>
     <row r="83" spans="2:10" ht="25.05" customHeight="1">
       <c r="B83" s="24"/>
-      <c r="C83" s="60" t="s">
+      <c r="C83" s="52" t="s">
         <v>265</v>
       </c>
-      <c r="D83" s="41" t="s">
+      <c r="D83" s="39" t="s">
         <v>211</v>
       </c>
       <c r="E83" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="F83" s="42" t="s">
+      <c r="F83" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="G83" s="43">
+      <c r="G83" s="41">
         <v>5</v>
       </c>
-      <c r="H83" s="40"/>
-      <c r="I83" s="44" t="s">
+      <c r="H83" s="38"/>
+      <c r="I83" s="42" t="s">
         <v>264</v>
       </c>
-      <c r="J83" s="37" t="s">
+      <c r="J83" s="43" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="84" spans="2:10" ht="25.05" customHeight="1">
       <c r="B84" s="24"/>
-      <c r="C84" s="60"/>
-      <c r="D84" s="41"/>
+      <c r="C84" s="52"/>
+      <c r="D84" s="39"/>
       <c r="E84" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="F84" s="42"/>
-      <c r="G84" s="43"/>
-      <c r="H84" s="40"/>
-      <c r="I84" s="44"/>
-      <c r="J84" s="37"/>
+      <c r="F84" s="40"/>
+      <c r="G84" s="41"/>
+      <c r="H84" s="38"/>
+      <c r="I84" s="42"/>
+      <c r="J84" s="43"/>
     </row>
     <row r="85" spans="2:10" ht="25.05" customHeight="1">
       <c r="B85" s="24"/>
-      <c r="C85" s="60"/>
-      <c r="D85" s="41"/>
+      <c r="C85" s="52"/>
+      <c r="D85" s="39"/>
       <c r="E85" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="F85" s="42"/>
-      <c r="G85" s="43"/>
-      <c r="H85" s="40"/>
-      <c r="I85" s="44"/>
-      <c r="J85" s="37"/>
+      <c r="F85" s="40"/>
+      <c r="G85" s="41"/>
+      <c r="H85" s="38"/>
+      <c r="I85" s="42"/>
+      <c r="J85" s="43"/>
     </row>
     <row r="86" spans="2:10" ht="25.05" customHeight="1">
       <c r="B86" s="24"/>
-      <c r="C86" s="60"/>
-      <c r="D86" s="41"/>
+      <c r="C86" s="52"/>
+      <c r="D86" s="39"/>
       <c r="E86" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="F86" s="42"/>
-      <c r="G86" s="43"/>
-      <c r="H86" s="40"/>
-      <c r="I86" s="44"/>
-      <c r="J86" s="37"/>
+      <c r="F86" s="40"/>
+      <c r="G86" s="41"/>
+      <c r="H86" s="38"/>
+      <c r="I86" s="42"/>
+      <c r="J86" s="43"/>
     </row>
     <row r="87" spans="2:10" ht="25.05" customHeight="1">
       <c r="B87" s="24"/>
-      <c r="C87" s="69"/>
-      <c r="D87" s="56"/>
+      <c r="C87" s="63"/>
+      <c r="D87" s="61"/>
       <c r="E87" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="F87" s="42"/>
-      <c r="G87" s="43"/>
-      <c r="H87" s="53"/>
-      <c r="I87" s="57"/>
+      <c r="F87" s="40"/>
+      <c r="G87" s="41"/>
+      <c r="H87" s="58"/>
+      <c r="I87" s="44"/>
       <c r="J87" s="45"/>
     </row>
     <row r="88" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B88" s="58" t="s">
+      <c r="B88" s="54" t="s">
         <v>217</v>
       </c>
-      <c r="C88" s="47" t="s">
+      <c r="C88" s="46" t="s">
         <v>167</v>
       </c>
-      <c r="D88" s="48" t="s">
+      <c r="D88" s="47" t="s">
         <v>175</v>
       </c>
-      <c r="E88" s="48" t="s">
+      <c r="E88" s="47" t="s">
         <v>193</v>
       </c>
-      <c r="F88" s="48" t="s">
+      <c r="F88" s="47" t="s">
         <v>192</v>
       </c>
-      <c r="G88" s="48">
+      <c r="G88" s="47">
         <v>3</v>
       </c>
-      <c r="H88" s="47"/>
-      <c r="I88" s="51" t="s">
+      <c r="H88" s="46"/>
+      <c r="I88" s="50" t="s">
         <v>259</v>
       </c>
-      <c r="J88" s="52" t="s">
+      <c r="J88" s="51" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="89" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B89" s="38"/>
-      <c r="C89" s="40"/>
-      <c r="D89" s="41"/>
-      <c r="E89" s="41"/>
-      <c r="F89" s="41"/>
-      <c r="G89" s="41"/>
-      <c r="H89" s="40"/>
-      <c r="I89" s="44"/>
-      <c r="J89" s="37"/>
+      <c r="B89" s="55"/>
+      <c r="C89" s="38"/>
+      <c r="D89" s="39"/>
+      <c r="E89" s="39"/>
+      <c r="F89" s="39"/>
+      <c r="G89" s="39"/>
+      <c r="H89" s="38"/>
+      <c r="I89" s="42"/>
+      <c r="J89" s="43"/>
     </row>
     <row r="90" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B90" s="38"/>
-      <c r="C90" s="40"/>
-      <c r="D90" s="41"/>
-      <c r="E90" s="41" t="s">
+      <c r="B90" s="55"/>
+      <c r="C90" s="38"/>
+      <c r="D90" s="39"/>
+      <c r="E90" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="F90" s="41" t="s">
+      <c r="F90" s="39" t="s">
         <v>195</v>
       </c>
-      <c r="G90" s="41" t="b">
+      <c r="G90" s="39" t="b">
         <v>1</v>
       </c>
-      <c r="H90" s="40"/>
-      <c r="I90" s="44"/>
-      <c r="J90" s="37"/>
+      <c r="H90" s="38"/>
+      <c r="I90" s="42"/>
+      <c r="J90" s="43"/>
     </row>
     <row r="91" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B91" s="38"/>
-      <c r="C91" s="40"/>
-      <c r="D91" s="41"/>
-      <c r="E91" s="41"/>
-      <c r="F91" s="41"/>
-      <c r="G91" s="41"/>
-      <c r="H91" s="40"/>
-      <c r="I91" s="44"/>
-      <c r="J91" s="37"/>
+      <c r="B91" s="55"/>
+      <c r="C91" s="38"/>
+      <c r="D91" s="39"/>
+      <c r="E91" s="39"/>
+      <c r="F91" s="39"/>
+      <c r="G91" s="39"/>
+      <c r="H91" s="38"/>
+      <c r="I91" s="42"/>
+      <c r="J91" s="43"/>
     </row>
     <row r="92" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B92" s="38"/>
-      <c r="C92" s="40" t="s">
+      <c r="B92" s="55"/>
+      <c r="C92" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="D92" s="41" t="s">
+      <c r="D92" s="39" t="s">
         <v>241</v>
       </c>
-      <c r="E92" s="41" t="s">
+      <c r="E92" s="39" t="s">
         <v>196</v>
       </c>
-      <c r="F92" s="41" t="s">
+      <c r="F92" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="G92" s="41">
+      <c r="G92" s="39">
         <v>3</v>
       </c>
-      <c r="H92" s="40"/>
-      <c r="I92" s="44" t="s">
+      <c r="H92" s="38"/>
+      <c r="I92" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="J92" s="37" t="s">
+      <c r="J92" s="43" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="93" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B93" s="38"/>
-      <c r="C93" s="40"/>
-      <c r="D93" s="41"/>
-      <c r="E93" s="41"/>
-      <c r="F93" s="41"/>
-      <c r="G93" s="41"/>
-      <c r="H93" s="40"/>
-      <c r="I93" s="44"/>
-      <c r="J93" s="37"/>
+      <c r="B93" s="55"/>
+      <c r="C93" s="38"/>
+      <c r="D93" s="39"/>
+      <c r="E93" s="39"/>
+      <c r="F93" s="39"/>
+      <c r="G93" s="39"/>
+      <c r="H93" s="38"/>
+      <c r="I93" s="42"/>
+      <c r="J93" s="43"/>
     </row>
     <row r="94" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B94" s="38"/>
-      <c r="C94" s="40"/>
-      <c r="D94" s="41"/>
-      <c r="E94" s="41" t="s">
+      <c r="B94" s="55"/>
+      <c r="C94" s="38"/>
+      <c r="D94" s="39"/>
+      <c r="E94" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="F94" s="41" t="s">
+      <c r="F94" s="39" t="s">
         <v>195</v>
       </c>
-      <c r="G94" s="41" t="b">
+      <c r="G94" s="39" t="b">
         <v>1</v>
       </c>
-      <c r="H94" s="40"/>
-      <c r="I94" s="44"/>
-      <c r="J94" s="37"/>
+      <c r="H94" s="38"/>
+      <c r="I94" s="42"/>
+      <c r="J94" s="43"/>
     </row>
     <row r="95" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B95" s="38"/>
-      <c r="C95" s="40"/>
-      <c r="D95" s="41"/>
-      <c r="E95" s="41"/>
-      <c r="F95" s="41"/>
-      <c r="G95" s="41"/>
-      <c r="H95" s="40"/>
-      <c r="I95" s="44"/>
-      <c r="J95" s="37"/>
+      <c r="B95" s="55"/>
+      <c r="C95" s="38"/>
+      <c r="D95" s="39"/>
+      <c r="E95" s="39"/>
+      <c r="F95" s="39"/>
+      <c r="G95" s="39"/>
+      <c r="H95" s="38"/>
+      <c r="I95" s="42"/>
+      <c r="J95" s="43"/>
     </row>
     <row r="96" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B96" s="38"/>
-      <c r="C96" s="40" t="s">
+      <c r="B96" s="55"/>
+      <c r="C96" s="38" t="s">
         <v>169</v>
       </c>
-      <c r="D96" s="41" t="s">
+      <c r="D96" s="39" t="s">
         <v>177</v>
       </c>
-      <c r="E96" s="41" t="s">
+      <c r="E96" s="39" t="s">
         <v>196</v>
       </c>
-      <c r="F96" s="41" t="s">
+      <c r="F96" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="G96" s="41">
+      <c r="G96" s="39">
         <v>3</v>
       </c>
-      <c r="H96" s="40"/>
-      <c r="I96" s="44" t="s">
+      <c r="H96" s="38"/>
+      <c r="I96" s="42" t="s">
         <v>260</v>
       </c>
-      <c r="J96" s="37" t="s">
+      <c r="J96" s="43" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="97" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B97" s="38"/>
-      <c r="C97" s="40"/>
-      <c r="D97" s="41"/>
-      <c r="E97" s="41"/>
-      <c r="F97" s="41"/>
-      <c r="G97" s="41"/>
-      <c r="H97" s="40"/>
-      <c r="I97" s="44"/>
-      <c r="J97" s="37"/>
+      <c r="B97" s="55"/>
+      <c r="C97" s="38"/>
+      <c r="D97" s="39"/>
+      <c r="E97" s="39"/>
+      <c r="F97" s="39"/>
+      <c r="G97" s="39"/>
+      <c r="H97" s="38"/>
+      <c r="I97" s="42"/>
+      <c r="J97" s="43"/>
     </row>
     <row r="98" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B98" s="38"/>
-      <c r="C98" s="40"/>
-      <c r="D98" s="41"/>
-      <c r="E98" s="41" t="s">
+      <c r="B98" s="55"/>
+      <c r="C98" s="38"/>
+      <c r="D98" s="39"/>
+      <c r="E98" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="F98" s="41" t="s">
+      <c r="F98" s="39" t="s">
         <v>195</v>
       </c>
-      <c r="G98" s="41" t="b">
+      <c r="G98" s="39" t="b">
         <v>0</v>
       </c>
-      <c r="H98" s="40"/>
-      <c r="I98" s="44"/>
-      <c r="J98" s="37"/>
+      <c r="H98" s="38"/>
+      <c r="I98" s="42"/>
+      <c r="J98" s="43"/>
     </row>
     <row r="99" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B99" s="38"/>
-      <c r="C99" s="40"/>
-      <c r="D99" s="41"/>
-      <c r="E99" s="41"/>
-      <c r="F99" s="41"/>
-      <c r="G99" s="41"/>
-      <c r="H99" s="40"/>
-      <c r="I99" s="44"/>
-      <c r="J99" s="37"/>
+      <c r="B99" s="55"/>
+      <c r="C99" s="38"/>
+      <c r="D99" s="39"/>
+      <c r="E99" s="39"/>
+      <c r="F99" s="39"/>
+      <c r="G99" s="39"/>
+      <c r="H99" s="38"/>
+      <c r="I99" s="42"/>
+      <c r="J99" s="43"/>
     </row>
     <row r="100" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B100" s="38"/>
-      <c r="C100" s="60" t="s">
+      <c r="B100" s="55"/>
+      <c r="C100" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="D100" s="41" t="s">
+      <c r="D100" s="39" t="s">
         <v>178</v>
       </c>
       <c r="E100" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="F100" s="41" t="s">
+      <c r="F100" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="G100" s="41">
+      <c r="G100" s="39">
         <v>5</v>
       </c>
-      <c r="H100" s="40"/>
-      <c r="I100" s="44" t="s">
+      <c r="H100" s="38"/>
+      <c r="I100" s="42" t="s">
         <v>261</v>
       </c>
-      <c r="J100" s="37" t="s">
+      <c r="J100" s="43" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="101" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B101" s="38"/>
-      <c r="C101" s="60"/>
-      <c r="D101" s="41"/>
+      <c r="B101" s="55"/>
+      <c r="C101" s="52"/>
+      <c r="D101" s="39"/>
       <c r="E101" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="F101" s="41"/>
-      <c r="G101" s="41"/>
-      <c r="H101" s="40"/>
-      <c r="I101" s="44"/>
-      <c r="J101" s="37"/>
+      <c r="F101" s="39"/>
+      <c r="G101" s="39"/>
+      <c r="H101" s="38"/>
+      <c r="I101" s="42"/>
+      <c r="J101" s="43"/>
     </row>
     <row r="102" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B102" s="38"/>
-      <c r="C102" s="60"/>
-      <c r="D102" s="41"/>
+      <c r="B102" s="55"/>
+      <c r="C102" s="52"/>
+      <c r="D102" s="39"/>
       <c r="E102" s="17" t="s">
         <v>198</v>
       </c>
@@ -7446,52 +7446,52 @@
       <c r="G102" s="31" t="b">
         <v>1</v>
       </c>
-      <c r="H102" s="40"/>
-      <c r="I102" s="44"/>
-      <c r="J102" s="37"/>
+      <c r="H102" s="38"/>
+      <c r="I102" s="42"/>
+      <c r="J102" s="43"/>
     </row>
     <row r="103" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B103" s="38"/>
-      <c r="C103" s="60" t="s">
+      <c r="B103" s="55"/>
+      <c r="C103" s="52" t="s">
         <v>171</v>
       </c>
-      <c r="D103" s="41" t="s">
+      <c r="D103" s="39" t="s">
         <v>212</v>
       </c>
       <c r="E103" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="F103" s="41" t="s">
+      <c r="F103" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="G103" s="41">
+      <c r="G103" s="39">
         <v>5</v>
       </c>
-      <c r="H103" s="40"/>
-      <c r="I103" s="44" t="s">
+      <c r="H103" s="38"/>
+      <c r="I103" s="42" t="s">
         <v>261</v>
       </c>
-      <c r="J103" s="37" t="s">
+      <c r="J103" s="43" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="104" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B104" s="38"/>
-      <c r="C104" s="60"/>
-      <c r="D104" s="41"/>
+      <c r="B104" s="55"/>
+      <c r="C104" s="52"/>
+      <c r="D104" s="39"/>
       <c r="E104" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="F104" s="41"/>
-      <c r="G104" s="41"/>
-      <c r="H104" s="40"/>
-      <c r="I104" s="44"/>
-      <c r="J104" s="37"/>
+      <c r="F104" s="39"/>
+      <c r="G104" s="39"/>
+      <c r="H104" s="38"/>
+      <c r="I104" s="42"/>
+      <c r="J104" s="43"/>
     </row>
     <row r="105" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B105" s="38"/>
-      <c r="C105" s="60"/>
-      <c r="D105" s="41"/>
+      <c r="B105" s="55"/>
+      <c r="C105" s="52"/>
+      <c r="D105" s="39"/>
       <c r="E105" s="17" t="s">
         <v>198</v>
       </c>
@@ -7501,76 +7501,262 @@
       <c r="G105" s="31" t="b">
         <v>1</v>
       </c>
-      <c r="H105" s="40"/>
-      <c r="I105" s="44"/>
-      <c r="J105" s="37"/>
+      <c r="H105" s="38"/>
+      <c r="I105" s="42"/>
+      <c r="J105" s="43"/>
     </row>
     <row r="106" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B106" s="38"/>
-      <c r="C106" s="40" t="s">
+      <c r="B106" s="55"/>
+      <c r="C106" s="38" t="s">
         <v>210</v>
       </c>
-      <c r="D106" s="41" t="s">
+      <c r="D106" s="39" t="s">
         <v>179</v>
       </c>
-      <c r="E106" s="41" t="s">
+      <c r="E106" s="39" t="s">
         <v>199</v>
       </c>
-      <c r="F106" s="41" t="s">
+      <c r="F106" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="G106" s="41">
+      <c r="G106" s="39">
         <v>3</v>
       </c>
-      <c r="H106" s="40"/>
-      <c r="I106" s="44" t="s">
+      <c r="H106" s="38"/>
+      <c r="I106" s="42" t="s">
         <v>260</v>
       </c>
-      <c r="J106" s="37" t="s">
+      <c r="J106" s="43" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="107" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B107" s="38"/>
-      <c r="C107" s="40"/>
-      <c r="D107" s="41"/>
-      <c r="E107" s="41"/>
-      <c r="F107" s="41"/>
-      <c r="G107" s="41"/>
-      <c r="H107" s="40"/>
-      <c r="I107" s="44"/>
-      <c r="J107" s="37"/>
+      <c r="B107" s="55"/>
+      <c r="C107" s="38"/>
+      <c r="D107" s="39"/>
+      <c r="E107" s="39"/>
+      <c r="F107" s="39"/>
+      <c r="G107" s="39"/>
+      <c r="H107" s="38"/>
+      <c r="I107" s="42"/>
+      <c r="J107" s="43"/>
     </row>
     <row r="108" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B108" s="38"/>
-      <c r="C108" s="40"/>
-      <c r="D108" s="41"/>
-      <c r="E108" s="41" t="s">
+      <c r="B108" s="55"/>
+      <c r="C108" s="38"/>
+      <c r="D108" s="39"/>
+      <c r="E108" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="F108" s="41" t="s">
+      <c r="F108" s="39" t="s">
         <v>195</v>
       </c>
-      <c r="G108" s="41" t="b">
+      <c r="G108" s="39" t="b">
         <v>1</v>
       </c>
-      <c r="H108" s="40"/>
-      <c r="I108" s="44"/>
-      <c r="J108" s="37"/>
+      <c r="H108" s="38"/>
+      <c r="I108" s="42"/>
+      <c r="J108" s="43"/>
     </row>
     <row r="109" spans="2:10" ht="25.05" customHeight="1">
-      <c r="B109" s="39"/>
-      <c r="C109" s="53"/>
-      <c r="D109" s="56"/>
-      <c r="E109" s="56"/>
-      <c r="F109" s="56"/>
-      <c r="G109" s="56"/>
-      <c r="H109" s="53"/>
-      <c r="I109" s="57"/>
+      <c r="B109" s="57"/>
+      <c r="C109" s="58"/>
+      <c r="D109" s="61"/>
+      <c r="E109" s="61"/>
+      <c r="F109" s="61"/>
+      <c r="G109" s="61"/>
+      <c r="H109" s="58"/>
+      <c r="I109" s="44"/>
       <c r="J109" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="210">
+    <mergeCell ref="C103:C105"/>
+    <mergeCell ref="D103:D105"/>
+    <mergeCell ref="C100:C102"/>
+    <mergeCell ref="D100:D102"/>
+    <mergeCell ref="J103:J105"/>
+    <mergeCell ref="J100:J102"/>
+    <mergeCell ref="F90:F91"/>
+    <mergeCell ref="G88:G89"/>
+    <mergeCell ref="G90:G91"/>
+    <mergeCell ref="H103:H105"/>
+    <mergeCell ref="I103:I105"/>
+    <mergeCell ref="I100:I102"/>
+    <mergeCell ref="H100:H102"/>
+    <mergeCell ref="F100:F101"/>
+    <mergeCell ref="G100:G101"/>
+    <mergeCell ref="I75:I77"/>
+    <mergeCell ref="F103:F104"/>
+    <mergeCell ref="G103:G104"/>
+    <mergeCell ref="E106:E107"/>
+    <mergeCell ref="E108:E109"/>
+    <mergeCell ref="F106:F107"/>
+    <mergeCell ref="G106:G107"/>
+    <mergeCell ref="F108:F109"/>
+    <mergeCell ref="G108:G109"/>
+    <mergeCell ref="E96:E97"/>
+    <mergeCell ref="F96:F97"/>
+    <mergeCell ref="G96:G97"/>
+    <mergeCell ref="E98:E99"/>
+    <mergeCell ref="F98:F99"/>
+    <mergeCell ref="G98:G99"/>
+    <mergeCell ref="E88:E89"/>
+    <mergeCell ref="F88:F89"/>
+    <mergeCell ref="E94:E95"/>
+    <mergeCell ref="F94:F95"/>
+    <mergeCell ref="G94:G95"/>
+    <mergeCell ref="E92:E93"/>
+    <mergeCell ref="F92:F93"/>
+    <mergeCell ref="G92:G93"/>
+    <mergeCell ref="H55:H58"/>
+    <mergeCell ref="F63:F66"/>
+    <mergeCell ref="G63:G66"/>
+    <mergeCell ref="F67:F70"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="F71:F74"/>
+    <mergeCell ref="G71:G74"/>
+    <mergeCell ref="F78:F82"/>
+    <mergeCell ref="G78:G82"/>
+    <mergeCell ref="H75:H77"/>
+    <mergeCell ref="J75:J77"/>
+    <mergeCell ref="F75:F77"/>
+    <mergeCell ref="G75:G77"/>
+    <mergeCell ref="C31:C34"/>
+    <mergeCell ref="D31:D34"/>
+    <mergeCell ref="H31:H34"/>
+    <mergeCell ref="G47:G50"/>
+    <mergeCell ref="F51:F54"/>
+    <mergeCell ref="G51:G54"/>
+    <mergeCell ref="C75:C77"/>
+    <mergeCell ref="D75:D77"/>
+    <mergeCell ref="F35:F38"/>
+    <mergeCell ref="G35:G38"/>
+    <mergeCell ref="F39:F42"/>
+    <mergeCell ref="G39:G42"/>
+    <mergeCell ref="F43:F46"/>
+    <mergeCell ref="G43:G46"/>
+    <mergeCell ref="F47:F50"/>
+    <mergeCell ref="I55:I58"/>
+    <mergeCell ref="J55:J58"/>
+    <mergeCell ref="C43:C46"/>
+    <mergeCell ref="C59:C62"/>
+    <mergeCell ref="D59:D62"/>
+    <mergeCell ref="J59:J62"/>
+    <mergeCell ref="H51:H54"/>
+    <mergeCell ref="J3:J6"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="J15:J18"/>
+    <mergeCell ref="J19:J22"/>
+    <mergeCell ref="J23:J26"/>
+    <mergeCell ref="J51:J54"/>
+    <mergeCell ref="I31:I34"/>
+    <mergeCell ref="I35:I38"/>
+    <mergeCell ref="I43:I46"/>
+    <mergeCell ref="I51:I54"/>
+    <mergeCell ref="H23:H26"/>
+    <mergeCell ref="H11:H14"/>
+    <mergeCell ref="H3:H6"/>
+    <mergeCell ref="J27:J30"/>
+    <mergeCell ref="J31:J34"/>
+    <mergeCell ref="J35:J38"/>
+    <mergeCell ref="J39:J42"/>
+    <mergeCell ref="J43:J46"/>
+    <mergeCell ref="I47:I50"/>
+    <mergeCell ref="J47:J50"/>
+    <mergeCell ref="H35:H38"/>
+    <mergeCell ref="H39:H42"/>
+    <mergeCell ref="B35:B62"/>
+    <mergeCell ref="H59:H62"/>
+    <mergeCell ref="I3:I6"/>
+    <mergeCell ref="I7:I10"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="I15:I18"/>
+    <mergeCell ref="I19:I22"/>
+    <mergeCell ref="I23:I26"/>
+    <mergeCell ref="B3:B14"/>
+    <mergeCell ref="B15:B34"/>
+    <mergeCell ref="C55:C58"/>
+    <mergeCell ref="D55:D58"/>
+    <mergeCell ref="I39:I42"/>
+    <mergeCell ref="C51:C54"/>
+    <mergeCell ref="D51:D54"/>
+    <mergeCell ref="I59:I62"/>
+    <mergeCell ref="F3:F6"/>
+    <mergeCell ref="G3:G6"/>
+    <mergeCell ref="F7:F10"/>
+    <mergeCell ref="G7:G10"/>
+    <mergeCell ref="F11:F14"/>
+    <mergeCell ref="G11:G14"/>
+    <mergeCell ref="F15:F18"/>
+    <mergeCell ref="I27:I30"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G23:G26"/>
+    <mergeCell ref="C47:C50"/>
+    <mergeCell ref="D47:D50"/>
+    <mergeCell ref="C27:C30"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="D7:D10"/>
+    <mergeCell ref="H43:H46"/>
+    <mergeCell ref="H47:H50"/>
+    <mergeCell ref="D35:D38"/>
+    <mergeCell ref="C35:C38"/>
+    <mergeCell ref="C39:C42"/>
+    <mergeCell ref="D39:D42"/>
+    <mergeCell ref="H27:H30"/>
+    <mergeCell ref="D27:D30"/>
+    <mergeCell ref="D43:D46"/>
+    <mergeCell ref="G27:G30"/>
+    <mergeCell ref="F31:F34"/>
+    <mergeCell ref="G31:G34"/>
+    <mergeCell ref="H7:H10"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="H67:H70"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="D15:D18"/>
+    <mergeCell ref="H15:H18"/>
+    <mergeCell ref="C19:C22"/>
+    <mergeCell ref="D19:D22"/>
+    <mergeCell ref="H19:H22"/>
+    <mergeCell ref="G15:G18"/>
+    <mergeCell ref="F19:F22"/>
+    <mergeCell ref="G19:G22"/>
+    <mergeCell ref="F55:F58"/>
+    <mergeCell ref="G55:G58"/>
+    <mergeCell ref="F59:F62"/>
+    <mergeCell ref="G59:G62"/>
+    <mergeCell ref="F27:F30"/>
+    <mergeCell ref="C23:C26"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="I67:I70"/>
+    <mergeCell ref="J67:J70"/>
+    <mergeCell ref="C63:C66"/>
+    <mergeCell ref="D63:D66"/>
+    <mergeCell ref="H63:H66"/>
+    <mergeCell ref="I63:I66"/>
+    <mergeCell ref="D71:D74"/>
+    <mergeCell ref="H71:H74"/>
+    <mergeCell ref="I71:I74"/>
+    <mergeCell ref="J63:J66"/>
+    <mergeCell ref="C83:C87"/>
+    <mergeCell ref="D83:D87"/>
+    <mergeCell ref="H83:H87"/>
+    <mergeCell ref="I83:I87"/>
+    <mergeCell ref="J83:J87"/>
+    <mergeCell ref="E90:E91"/>
+    <mergeCell ref="C78:C82"/>
+    <mergeCell ref="D78:D82"/>
+    <mergeCell ref="H78:H82"/>
+    <mergeCell ref="I78:I82"/>
+    <mergeCell ref="J78:J82"/>
+    <mergeCell ref="F83:F87"/>
+    <mergeCell ref="G83:G87"/>
     <mergeCell ref="B63:B81"/>
     <mergeCell ref="C106:C109"/>
     <mergeCell ref="D106:D109"/>
@@ -7595,192 +7781,6 @@
     <mergeCell ref="I96:I99"/>
     <mergeCell ref="J71:J74"/>
     <mergeCell ref="C71:C74"/>
-    <mergeCell ref="C83:C87"/>
-    <mergeCell ref="D83:D87"/>
-    <mergeCell ref="H83:H87"/>
-    <mergeCell ref="I83:I87"/>
-    <mergeCell ref="J83:J87"/>
-    <mergeCell ref="E90:E91"/>
-    <mergeCell ref="C78:C82"/>
-    <mergeCell ref="D78:D82"/>
-    <mergeCell ref="H78:H82"/>
-    <mergeCell ref="I78:I82"/>
-    <mergeCell ref="J78:J82"/>
-    <mergeCell ref="F83:F87"/>
-    <mergeCell ref="G83:G87"/>
-    <mergeCell ref="I67:I70"/>
-    <mergeCell ref="J67:J70"/>
-    <mergeCell ref="C63:C66"/>
-    <mergeCell ref="D63:D66"/>
-    <mergeCell ref="H63:H66"/>
-    <mergeCell ref="I63:I66"/>
-    <mergeCell ref="D71:D74"/>
-    <mergeCell ref="H71:H74"/>
-    <mergeCell ref="I71:I74"/>
-    <mergeCell ref="J63:J66"/>
-    <mergeCell ref="H7:H10"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="H67:H70"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="D15:D18"/>
-    <mergeCell ref="H15:H18"/>
-    <mergeCell ref="C19:C22"/>
-    <mergeCell ref="D19:D22"/>
-    <mergeCell ref="H19:H22"/>
-    <mergeCell ref="G15:G18"/>
-    <mergeCell ref="F19:F22"/>
-    <mergeCell ref="G19:G22"/>
-    <mergeCell ref="F55:F58"/>
-    <mergeCell ref="G55:G58"/>
-    <mergeCell ref="F59:F62"/>
-    <mergeCell ref="G59:G62"/>
-    <mergeCell ref="F27:F30"/>
-    <mergeCell ref="C23:C26"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="G23:G26"/>
-    <mergeCell ref="C47:C50"/>
-    <mergeCell ref="D47:D50"/>
-    <mergeCell ref="C27:C30"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="D7:D10"/>
-    <mergeCell ref="H43:H46"/>
-    <mergeCell ref="H47:H50"/>
-    <mergeCell ref="D35:D38"/>
-    <mergeCell ref="C35:C38"/>
-    <mergeCell ref="C39:C42"/>
-    <mergeCell ref="D39:D42"/>
-    <mergeCell ref="H27:H30"/>
-    <mergeCell ref="D27:D30"/>
-    <mergeCell ref="D43:D46"/>
-    <mergeCell ref="G27:G30"/>
-    <mergeCell ref="F31:F34"/>
-    <mergeCell ref="G31:G34"/>
-    <mergeCell ref="B35:B62"/>
-    <mergeCell ref="H59:H62"/>
-    <mergeCell ref="I3:I6"/>
-    <mergeCell ref="I7:I10"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="I15:I18"/>
-    <mergeCell ref="I19:I22"/>
-    <mergeCell ref="I23:I26"/>
-    <mergeCell ref="B3:B14"/>
-    <mergeCell ref="B15:B34"/>
-    <mergeCell ref="C55:C58"/>
-    <mergeCell ref="D55:D58"/>
-    <mergeCell ref="I39:I42"/>
-    <mergeCell ref="C51:C54"/>
-    <mergeCell ref="D51:D54"/>
-    <mergeCell ref="I59:I62"/>
-    <mergeCell ref="F3:F6"/>
-    <mergeCell ref="G3:G6"/>
-    <mergeCell ref="F7:F10"/>
-    <mergeCell ref="G7:G10"/>
-    <mergeCell ref="F11:F14"/>
-    <mergeCell ref="G11:G14"/>
-    <mergeCell ref="F15:F18"/>
-    <mergeCell ref="I27:I30"/>
-    <mergeCell ref="H51:H54"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="J15:J18"/>
-    <mergeCell ref="J19:J22"/>
-    <mergeCell ref="J23:J26"/>
-    <mergeCell ref="J51:J54"/>
-    <mergeCell ref="I31:I34"/>
-    <mergeCell ref="I35:I38"/>
-    <mergeCell ref="I43:I46"/>
-    <mergeCell ref="I51:I54"/>
-    <mergeCell ref="H23:H26"/>
-    <mergeCell ref="H11:H14"/>
-    <mergeCell ref="H3:H6"/>
-    <mergeCell ref="J27:J30"/>
-    <mergeCell ref="J31:J34"/>
-    <mergeCell ref="J35:J38"/>
-    <mergeCell ref="J39:J42"/>
-    <mergeCell ref="J43:J46"/>
-    <mergeCell ref="I47:I50"/>
-    <mergeCell ref="J47:J50"/>
-    <mergeCell ref="H35:H38"/>
-    <mergeCell ref="H39:H42"/>
-    <mergeCell ref="J75:J77"/>
-    <mergeCell ref="F75:F77"/>
-    <mergeCell ref="G75:G77"/>
-    <mergeCell ref="C31:C34"/>
-    <mergeCell ref="D31:D34"/>
-    <mergeCell ref="H31:H34"/>
-    <mergeCell ref="G47:G50"/>
-    <mergeCell ref="F51:F54"/>
-    <mergeCell ref="G51:G54"/>
-    <mergeCell ref="C75:C77"/>
-    <mergeCell ref="D75:D77"/>
-    <mergeCell ref="F35:F38"/>
-    <mergeCell ref="G35:G38"/>
-    <mergeCell ref="F39:F42"/>
-    <mergeCell ref="G39:G42"/>
-    <mergeCell ref="F43:F46"/>
-    <mergeCell ref="G43:G46"/>
-    <mergeCell ref="F47:F50"/>
-    <mergeCell ref="I55:I58"/>
-    <mergeCell ref="J55:J58"/>
-    <mergeCell ref="C43:C46"/>
-    <mergeCell ref="C59:C62"/>
-    <mergeCell ref="D59:D62"/>
-    <mergeCell ref="J59:J62"/>
-    <mergeCell ref="H55:H58"/>
-    <mergeCell ref="F63:F66"/>
-    <mergeCell ref="G63:G66"/>
-    <mergeCell ref="F67:F70"/>
-    <mergeCell ref="G67:G70"/>
-    <mergeCell ref="F71:F74"/>
-    <mergeCell ref="G71:G74"/>
-    <mergeCell ref="F78:F82"/>
-    <mergeCell ref="G78:G82"/>
-    <mergeCell ref="H75:H77"/>
-    <mergeCell ref="I75:I77"/>
-    <mergeCell ref="F103:F104"/>
-    <mergeCell ref="G103:G104"/>
-    <mergeCell ref="E106:E107"/>
-    <mergeCell ref="E108:E109"/>
-    <mergeCell ref="F106:F107"/>
-    <mergeCell ref="G106:G107"/>
-    <mergeCell ref="F108:F109"/>
-    <mergeCell ref="G108:G109"/>
-    <mergeCell ref="E96:E97"/>
-    <mergeCell ref="F96:F97"/>
-    <mergeCell ref="G96:G97"/>
-    <mergeCell ref="E98:E99"/>
-    <mergeCell ref="F98:F99"/>
-    <mergeCell ref="G98:G99"/>
-    <mergeCell ref="E88:E89"/>
-    <mergeCell ref="F88:F89"/>
-    <mergeCell ref="E94:E95"/>
-    <mergeCell ref="F94:F95"/>
-    <mergeCell ref="G94:G95"/>
-    <mergeCell ref="E92:E93"/>
-    <mergeCell ref="F92:F93"/>
-    <mergeCell ref="G92:G93"/>
-    <mergeCell ref="C103:C105"/>
-    <mergeCell ref="D103:D105"/>
-    <mergeCell ref="C100:C102"/>
-    <mergeCell ref="D100:D102"/>
-    <mergeCell ref="J103:J105"/>
-    <mergeCell ref="J100:J102"/>
-    <mergeCell ref="F90:F91"/>
-    <mergeCell ref="G88:G89"/>
-    <mergeCell ref="G90:G91"/>
-    <mergeCell ref="H103:H105"/>
-    <mergeCell ref="I103:I105"/>
-    <mergeCell ref="I100:I102"/>
-    <mergeCell ref="H100:H102"/>
-    <mergeCell ref="F100:F101"/>
-    <mergeCell ref="G100:G101"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/description/TC 설계서.xlsx
+++ b/description/TC 설계서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suresoft\Documents\sure_rust_project\description\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5763C3AF-16BC-4C5E-BE5A-0D627C7D5739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C431D473-B1BA-435E-A5F0-5BF928A3B834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44955" yWindow="4080" windowWidth="20055" windowHeight="13620" tabRatio="291" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38910" yWindow="5115" windowWidth="20205" windowHeight="14250" tabRatio="311" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="최소 TC 조합" sheetId="4" r:id="rId1"/>
@@ -7691,7 +7691,6 @@
     <mergeCell ref="G11:G14"/>
     <mergeCell ref="F15:F18"/>
     <mergeCell ref="I27:I30"/>
-    <mergeCell ref="F23:F26"/>
     <mergeCell ref="G23:G26"/>
     <mergeCell ref="C47:C50"/>
     <mergeCell ref="D47:D50"/>
@@ -7734,6 +7733,7 @@
     <mergeCell ref="F27:F30"/>
     <mergeCell ref="C23:C26"/>
     <mergeCell ref="D23:D26"/>
+    <mergeCell ref="F23:F26"/>
     <mergeCell ref="I67:I70"/>
     <mergeCell ref="J67:J70"/>
     <mergeCell ref="C63:C66"/>
